--- a/testdata/QA Scenario - Sales STD PRICE.xlsx
+++ b/testdata/QA Scenario - Sales STD PRICE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="5" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535"/>
   </bookViews>
   <sheets>
     <sheet name="Case 1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="93">
   <si>
     <t>Item</t>
   </si>
@@ -1388,86 +1388,86 @@
       <c r="L5" s="33">
         <v>0</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="33">
         <f>I5</f>
         <v>15000</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="33">
         <f>ROUND((M5*J5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <f>I5-N5</f>
         <v>15000</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="33">
         <f>ROUND((O5*K5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="33">
         <f>ROUND(O5-P5,2)</f>
         <v>15000</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="33">
         <f>ROUND((Q5*L5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="33">
         <f>N5+P5+R5</f>
         <v>0</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="33">
         <f>S5/G5</f>
         <v>0</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="33">
         <f>(I5-S5)</f>
         <v>15000</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="V5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W5" s="30">
         <v>0.12</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="29">
+      <c r="Z5" s="33">
         <f>IF($D$3=2,ROUND(((U5*W5)),2),0)</f>
         <v>1800</v>
       </c>
-      <c r="AA5" s="29">
+      <c r="AA5" s="33">
         <f>X5+Y5+Z5</f>
         <v>1800</v>
       </c>
-      <c r="AB5" s="29">
+      <c r="AB5" s="33">
         <f t="shared" ref="AB5" si="0">U5+AA5</f>
         <v>16800</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="33">
         <v>120</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="33">
         <f t="shared" ref="AD5" si="1">U5*$N$3</f>
         <v>15000</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <v>1</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="33">
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
-      <c r="AG5" s="38" t="s">
+      <c r="AG5" t="s" s="38">
         <v>87</v>
       </c>
-      <c r="AH5" s="38" t="s">
+      <c r="AH5" t="s" s="38">
         <v>55</v>
       </c>
       <c r="AI5" s="29">
@@ -1526,91 +1526,91 @@
       <c r="L6" s="33">
         <v>0</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="33">
         <f>I6</f>
         <v>20000</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="33">
         <f>ROUND((M6*J6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="33">
         <f>I6-N6</f>
         <v>20000</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="33">
         <f>ROUND((O6*K6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="33">
         <f>ROUND(O6-P6,2)</f>
         <v>20000</v>
       </c>
-      <c r="R6" s="29">
+      <c r="R6" s="33">
         <f>ROUND((Q6*L6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="31">
+      <c r="S6" s="33">
         <f>N6+P6+R6</f>
         <v>0</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="33">
         <f>S6/G6</f>
         <v>0</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="33">
         <f>(I6-S6)</f>
         <v>20000</v>
       </c>
-      <c r="V6" s="29" t="s">
+      <c r="V6" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W6" s="30">
         <v>0.05</v>
       </c>
-      <c r="X6" s="29">
+      <c r="X6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="29">
+      <c r="Y6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="29">
+      <c r="Z6" s="33">
         <f>IF($D$3=2,ROUND(((U6*W6)),2),0)</f>
         <v>1000</v>
       </c>
-      <c r="AA6" s="29">
+      <c r="AA6" s="33">
         <f>X6+Y6+Z6</f>
         <v>1000</v>
       </c>
-      <c r="AB6" s="29">
+      <c r="AB6" s="33">
         <f t="shared" ref="AB6" si="3">U6+AA6</f>
         <v>21000</v>
       </c>
-      <c r="AC6" s="29">
+      <c r="AC6" s="33">
         <v>120</v>
       </c>
-      <c r="AD6" s="29">
+      <c r="AD6" s="33">
         <f t="shared" ref="AD6" si="4">U6*$N$3</f>
         <v>20000</v>
       </c>
-      <c r="AE6" s="32">
+      <c r="AE6" s="33">
         <v>3</v>
       </c>
-      <c r="AF6" s="32">
+      <c r="AF6" s="33">
         <f>ROUND(G6/AE6,3)</f>
         <v>3.3330000000000002</v>
       </c>
-      <c r="AG6" s="38" t="s">
+      <c r="AG6" t="s" s="38">
         <v>88</v>
       </c>
-      <c r="AH6" s="38" t="s">
+      <c r="AH6" t="s" s="38">
         <v>56</v>
       </c>
       <c r="AI6" s="29">
         <f>ROUND((AG6-AF6),3)</f>
-        <v>1375.002</v>
+        <v>1371.6690000000001</v>
       </c>
       <c r="AJ6" s="27" t="s">
         <v>50</v>
@@ -1723,7 +1723,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AM8"/>
+  <dimension ref="A1:AM12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
@@ -2046,57 +2046,57 @@
       <c r="L5" s="33">
         <v>10</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="33">
         <f>I5</f>
         <v>15000</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="33">
         <f>ROUND((M5*J5)/100,2)</f>
         <v>1500</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <f>I5-N5</f>
         <v>13500</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="33">
         <f>ROUND((O5*K5)/100,2)</f>
         <v>1350</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="33">
         <f>ROUND(O5-P5,2)</f>
         <v>12150</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="33">
         <f>ROUND((Q5*L5)/100,2)</f>
         <v>1215</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="33">
         <f>ROUND(N5+P5+R5,2)</f>
         <v>4065</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="33">
         <f>S5/G5</f>
         <v>406.5</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="33">
         <f>(I5-S5)</f>
         <v>10935</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="V5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W5" s="30">
         <v>0.12</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="29">
+      <c r="Z5" s="33">
         <f>IF($D$3=2,ROUND(((U5*W5)),2),0)</f>
         <v>1312.2</v>
       </c>
@@ -2104,21 +2104,21 @@
         <f>ROUND((X5+Y5+Z5+AM5),2)</f>
         <v>1312.2</v>
       </c>
-      <c r="AB5" s="29">
+      <c r="AB5" s="33">
         <f t="shared" ref="AB5:AB6" si="0">U5+AA5</f>
         <v>12247.2</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="33">
         <v>120</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="33">
         <f t="shared" ref="AD5:AD6" si="1">U5*$N$3</f>
         <v>10935</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <v>1</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="33">
         <f>G5/AE5</f>
         <v>10</v>
       </c>
@@ -2184,57 +2184,57 @@
       <c r="L6" s="33">
         <v>0</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="33">
         <f>I6</f>
         <v>20000</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="33">
         <f>ROUND((M6*J6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="33">
         <f>I6-N6</f>
         <v>20000</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="33">
         <f>ROUND((O6*K6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="33">
         <f>ROUND(O6-P6,2)</f>
         <v>20000</v>
       </c>
-      <c r="R6" s="29">
+      <c r="R6" s="33">
         <f>ROUND((Q6*L6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="31">
+      <c r="S6" s="33">
         <f>ROUND(N6+P6+R6,2)</f>
         <v>0</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="33">
         <f>S6/G6</f>
         <v>0</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="33">
         <f>(I6-S6)</f>
         <v>20000</v>
       </c>
-      <c r="V6" s="29" t="s">
+      <c r="V6" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W6" s="30">
         <v>0.12</v>
       </c>
-      <c r="X6" s="29">
+      <c r="X6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="29">
+      <c r="Y6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="29">
+      <c r="Z6" s="33">
         <f>IF($D$3=2,ROUND(((U6*W6)),2),0)</f>
         <v>2400</v>
       </c>
@@ -2242,21 +2242,21 @@
         <f>ROUND((X6+Y6+Z6+AM6),2)</f>
         <v>3600</v>
       </c>
-      <c r="AB6" s="29">
+      <c r="AB6" s="33">
         <f t="shared" si="0"/>
         <v>23600</v>
       </c>
-      <c r="AC6" s="29">
+      <c r="AC6" s="33">
         <v>120</v>
       </c>
-      <c r="AD6" s="29">
+      <c r="AD6" s="33">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="AE6" s="32">
+      <c r="AE6" s="33">
         <v>3</v>
       </c>
-      <c r="AF6" s="32">
+      <c r="AF6" s="33">
         <f>ROUND(G6/AE6,3)</f>
         <v>3.3330000000000002</v>
       </c>
@@ -2367,6 +2367,9 @@
       <c r="AF8" s="13"/>
       <c r="AG8" s="13"/>
       <c r="AH8" s="13"/>
+    </row>
+    <row r="12" spans="1:39">
+      <c r="J12" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2707,39 +2710,39 @@
       <c r="L5" s="33">
         <v>0</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="33">
         <f>I5</f>
         <v>15000</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="33">
         <f>ROUND((M5*J5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <f>I5-N5</f>
         <v>15000</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="33">
         <f>ROUND((O5*K5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="33">
         <f>ROUND(O5-P5,2)</f>
         <v>15000</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="33">
         <f>ROUND((Q5*L5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="33">
         <f>N5+P5+R5</f>
         <v>0</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="33">
         <f>S5/G5</f>
         <v>0</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="33">
         <f>(I5-S5)</f>
         <v>15000</v>
       </c>
@@ -2749,37 +2752,37 @@
       <c r="W5" s="30">
         <v>0.12</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="29">
+      <c r="Z5" s="33">
         <f>IF($D$3=2,ROUND(((U5*W5)),2),0)</f>
         <v>1800</v>
       </c>
-      <c r="AA5" s="29">
+      <c r="AA5" s="33">
         <f>X5+Y5+Z5</f>
         <v>1800</v>
       </c>
-      <c r="AB5" s="29">
+      <c r="AB5" s="33">
         <f t="shared" ref="AB5:AB6" si="0">U5+AA5</f>
         <v>16800</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="33">
         <v>120</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="33">
         <f t="shared" ref="AD5:AD6" si="1">U5*$N$3</f>
         <v>15000</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <v>1</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="33">
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
@@ -2846,39 +2849,39 @@
       <c r="L6" s="33">
         <v>0</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="33">
         <f>I6</f>
         <v>20000</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="33">
         <f>ROUND((M6*J6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="33">
         <f>I6-N6</f>
         <v>20000</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="33">
         <f>ROUND((O6*K6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="33">
         <f>ROUND(O6-P6,2)</f>
         <v>20000</v>
       </c>
-      <c r="R6" s="29">
+      <c r="R6" s="33">
         <f>ROUND((Q6*L6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="31">
+      <c r="S6" s="33">
         <f>N6+P6+R6</f>
         <v>0</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="33">
         <f>S6/G6</f>
         <v>0</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="33">
         <f>(I6-S6)</f>
         <v>20000</v>
       </c>
@@ -2888,37 +2891,37 @@
       <c r="W6" s="30">
         <v>0.05</v>
       </c>
-      <c r="X6" s="29">
+      <c r="X6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="29">
+      <c r="Y6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="29">
+      <c r="Z6" s="33">
         <f>IF($D$3=2,ROUND(((U6*W6)),2),0)</f>
         <v>1000</v>
       </c>
-      <c r="AA6" s="29">
+      <c r="AA6" s="33">
         <f>X6+Y6+Z6</f>
         <v>1000</v>
       </c>
-      <c r="AB6" s="29">
+      <c r="AB6" s="33">
         <f t="shared" si="0"/>
         <v>21000</v>
       </c>
-      <c r="AC6" s="29">
+      <c r="AC6" s="33">
         <v>120</v>
       </c>
-      <c r="AD6" s="29">
+      <c r="AD6" s="33">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="AE6" s="32">
+      <c r="AE6" s="33">
         <v>3</v>
       </c>
-      <c r="AF6" s="32">
+      <c r="AF6" s="33">
         <f>ROUND(G6/AE6,3)</f>
         <v>3.3330000000000002</v>
       </c>
@@ -2930,7 +2933,7 @@
       </c>
       <c r="AI6" s="29">
         <f>ROUND((AG6-AF6),3)</f>
-        <v>1375.002</v>
+        <v>1371.6690000000001</v>
       </c>
       <c r="AJ6" s="27" t="s">
         <v>50</v>
@@ -5218,79 +5221,79 @@
       <c r="L5" s="33">
         <v>0</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="33">
         <f>I5</f>
         <v>15000</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="33">
         <f>ROUND((M5*J5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <f>I5-N5</f>
         <v>15000</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="33">
         <f>ROUND((O5*K5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="33">
         <f>ROUND(O5-P5,2)</f>
         <v>15000</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="33">
         <f>ROUND((Q5*L5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="33">
         <f>N5+P5+R5</f>
         <v>0</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="33">
         <f>S5/G5</f>
         <v>0</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="33">
         <f>(I5-S5)</f>
         <v>15000</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="V5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W5" s="30">
         <v>0.12</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="29">
+      <c r="Z5" s="33">
         <f>IF($D$3=2,ROUND(((U5*W5)),2),0)</f>
         <v>1800</v>
       </c>
-      <c r="AA5" s="29">
+      <c r="AA5" s="33">
         <f>X5+Y5+Z5</f>
         <v>1800</v>
       </c>
-      <c r="AB5" s="29">
+      <c r="AB5" s="33">
         <f t="shared" ref="AB5:AB6" si="0">U5+AA5</f>
         <v>16800</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="33">
         <v>120</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="33">
         <f t="shared" ref="AD5:AD6" si="1">U5*$N$3</f>
         <v>15000</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <v>1</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="33">
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
@@ -5356,79 +5359,79 @@
       <c r="L6" s="33">
         <v>0</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="33">
         <f>I6</f>
         <v>20000</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="33">
         <f>ROUND((M6*J6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="33">
         <f>I6-N6</f>
         <v>20000</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="33">
         <f>ROUND((O6*K6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="33">
         <f>ROUND(O6-P6,2)</f>
         <v>20000</v>
       </c>
-      <c r="R6" s="29">
+      <c r="R6" s="33">
         <f>ROUND((Q6*L6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="31">
+      <c r="S6" s="33">
         <f>N6+P6+R6</f>
         <v>0</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="33">
         <f>S6/G6</f>
         <v>0</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="33">
         <f>(I6-S6)</f>
         <v>20000</v>
       </c>
-      <c r="V6" s="29" t="s">
+      <c r="V6" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W6" s="30">
         <v>0.05</v>
       </c>
-      <c r="X6" s="29">
+      <c r="X6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="29">
+      <c r="Y6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="29">
+      <c r="Z6" s="33">
         <f>IF($D$3=2,ROUND(((U6*W6)),2),0)</f>
         <v>1000</v>
       </c>
-      <c r="AA6" s="29">
+      <c r="AA6" s="33">
         <f>X6+Y6+Z6</f>
         <v>1000</v>
       </c>
-      <c r="AB6" s="29">
+      <c r="AB6" s="33">
         <f t="shared" si="0"/>
         <v>21000</v>
       </c>
-      <c r="AC6" s="29">
+      <c r="AC6" s="33">
         <v>120</v>
       </c>
-      <c r="AD6" s="29">
+      <c r="AD6" s="33">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="AE6" s="32">
+      <c r="AE6" s="33">
         <v>3</v>
       </c>
-      <c r="AF6" s="32">
+      <c r="AF6" s="33">
         <f>ROUND(G6/AE6,3)</f>
         <v>3.3330000000000002</v>
       </c>
@@ -5440,7 +5443,7 @@
       </c>
       <c r="AI6" s="29">
         <f>ROUND((AG6-AF6),3)</f>
-        <v>1375.002</v>
+        <v>1371.6690000000001</v>
       </c>
       <c r="AJ6" s="27" t="s">
         <v>50</v>
@@ -5876,79 +5879,79 @@
       <c r="L5" s="33">
         <v>0</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="33">
         <f>I5</f>
         <v>15000</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="33">
         <f>ROUND((M5*J5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <f>I5-N5</f>
         <v>15000</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="33">
         <f>ROUND((O5*K5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="33">
         <f>ROUND(O5-P5,2)</f>
         <v>15000</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="33">
         <f>ROUND((Q5*L5)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="33">
         <f>N5+P5+R5</f>
         <v>0</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="33">
         <f>S5/G5</f>
         <v>0</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="33">
         <f>(I5-S5)</f>
         <v>15000</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="V5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W5" s="30">
         <v>0.12</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="29">
+      <c r="Z5" s="33">
         <f>IF($D$3=2,ROUND(((U5*W5)),2),0)</f>
         <v>1800</v>
       </c>
-      <c r="AA5" s="29">
+      <c r="AA5" s="33">
         <f>X5+Y5+Z5</f>
         <v>1800</v>
       </c>
-      <c r="AB5" s="29">
+      <c r="AB5" s="33">
         <f t="shared" ref="AB5:AB6" si="0">U5+AA5</f>
         <v>16800</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="33">
         <v>120</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="33">
         <f t="shared" ref="AD5:AD6" si="1">U5*$N$3</f>
         <v>15000</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <v>1</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="33">
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
@@ -6014,79 +6017,79 @@
       <c r="L6" s="33">
         <v>0</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="33">
         <f>I6</f>
         <v>20000</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="33">
         <f>ROUND((M6*J6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="33">
         <f>I6-N6</f>
         <v>20000</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="33">
         <f>ROUND((O6*K6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="33">
         <f>ROUND(O6-P6,2)</f>
         <v>20000</v>
       </c>
-      <c r="R6" s="29">
+      <c r="R6" s="33">
         <f>ROUND((Q6*L6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="31">
+      <c r="S6" s="33">
         <f>N6+P6+R6</f>
         <v>0</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="33">
         <f>S6/G6</f>
         <v>0</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="33">
         <f>(I6-S6)</f>
         <v>20000</v>
       </c>
-      <c r="V6" s="29" t="s">
+      <c r="V6" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W6" s="30">
         <v>0.05</v>
       </c>
-      <c r="X6" s="29">
+      <c r="X6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="29">
+      <c r="Y6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="29">
+      <c r="Z6" s="33">
         <f>IF($D$3=2,ROUND(((U6*W6)),2),0)</f>
         <v>1000</v>
       </c>
-      <c r="AA6" s="29">
+      <c r="AA6" s="33">
         <f>X6+Y6+Z6</f>
         <v>1000</v>
       </c>
-      <c r="AB6" s="29">
+      <c r="AB6" s="33">
         <f t="shared" si="0"/>
         <v>21000</v>
       </c>
-      <c r="AC6" s="29">
+      <c r="AC6" s="33">
         <v>120</v>
       </c>
-      <c r="AD6" s="29">
+      <c r="AD6" s="33">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="AE6" s="32">
+      <c r="AE6" s="33">
         <v>3</v>
       </c>
-      <c r="AF6" s="32">
+      <c r="AF6" s="33">
         <f>ROUND(G6/AE6,3)</f>
         <v>3.3330000000000002</v>
       </c>
@@ -6098,7 +6101,7 @@
       </c>
       <c r="AI6" s="29">
         <f>ROUND((AG6-AF6),3)</f>
-        <v>1375.002</v>
+        <v>1371.6690000000001</v>
       </c>
       <c r="AJ6" s="27" t="s">
         <v>50</v>
@@ -6534,79 +6537,79 @@
       <c r="L5" s="33">
         <v>20</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="33">
         <f>I5</f>
         <v>15000</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="33">
         <f>ROUND((M5*J5)/100,2)</f>
         <v>1500</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <f>I5-N5</f>
         <v>13500</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="33">
         <f>ROUND((O5*K5)/100,2)</f>
         <v>2025</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="33">
         <f>ROUND(O5-P5,2)</f>
         <v>11475</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="33">
         <f>ROUND((Q5*L5)/100,2)</f>
         <v>2295</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="33">
         <f>N5+P5+R5</f>
         <v>5820</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="33">
         <f>S5/G5</f>
         <v>582</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="33">
         <f>(I5-S5)</f>
         <v>9180</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="V5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W5" s="30">
         <v>0.05</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="29">
+      <c r="Z5" s="33">
         <f>IF($D$3=2,ROUND(((U5*W5)),2),0)</f>
         <v>459</v>
       </c>
-      <c r="AA5" s="29">
+      <c r="AA5" s="33">
         <f>X5+Y5+Z5</f>
         <v>459</v>
       </c>
-      <c r="AB5" s="29">
+      <c r="AB5" s="33">
         <f t="shared" ref="AB5" si="0">U5+AA5</f>
         <v>9639</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="33">
         <v>120</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="33">
         <f t="shared" ref="AD5" si="1">U5*$N$3</f>
         <v>9180</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <v>1</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="33">
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
@@ -7061,79 +7064,79 @@
       <c r="L5" s="33">
         <v>20</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="33">
         <f>I5</f>
         <v>15000</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="33">
         <f>ROUND((M5*J5)/100,2)</f>
         <v>1500</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <f>I5-N5</f>
         <v>13500</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="33">
         <f>ROUND((O5*K5)/100,2)</f>
         <v>2025</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="33">
         <f>ROUND(O5-P5,2)</f>
         <v>11475</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="33">
         <f>ROUND((Q5*L5)/100,2)</f>
         <v>2295</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="33">
         <f>N5+P5+R5</f>
         <v>5820</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="33">
         <f>S5/G5</f>
         <v>582</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="33">
         <f>(I5-S5)</f>
         <v>9180</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="V5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W5" s="30">
         <v>0.05</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="29">
+      <c r="Z5" s="33">
         <f>IF($D$3=2,ROUND(((U5*W5)),2),0)</f>
         <v>459</v>
       </c>
-      <c r="AA5" s="29">
+      <c r="AA5" s="33">
         <f>X5+Y5+Z5</f>
         <v>459</v>
       </c>
-      <c r="AB5" s="29">
+      <c r="AB5" s="33">
         <f t="shared" ref="AB5" si="0">U5+AA5</f>
         <v>9639</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="33">
         <v>120</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="33">
         <f t="shared" ref="AD5" si="1">U5*$N$3</f>
         <v>9180</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <v>1</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="33">
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
@@ -7588,79 +7591,79 @@
       <c r="L5" s="33">
         <v>20</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="33">
         <f>I5</f>
         <v>15000</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="33">
         <f>ROUND((M5*J5)/100,2)</f>
         <v>1500</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <f>I5-N5</f>
         <v>13500</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="33">
         <f>ROUND((O5*K5)/100,2)</f>
         <v>1620</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="33">
         <f>ROUND(O5-P5,2)</f>
         <v>11880</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="33">
         <f>ROUND((Q5*L5)/100,2)</f>
         <v>2376</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="33">
         <f>N5+P5+R5</f>
         <v>5496</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="33">
         <f>S5/G5</f>
         <v>549.6</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="33">
         <f>(I5-S5)</f>
         <v>9504</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="V5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W5" s="30">
         <v>0.12</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="29">
+      <c r="Z5" s="33">
         <f>ROUND(IF($D$3=2,((U5*W5)),0),2)</f>
         <v>1140.48</v>
       </c>
-      <c r="AA5" s="29">
+      <c r="AA5" s="33">
         <f>X5+Y5+Z5</f>
         <v>1140.48</v>
       </c>
-      <c r="AB5" s="29">
+      <c r="AB5" s="33">
         <f t="shared" ref="AB5:AB6" si="0">U5+AA5</f>
         <v>10644.48</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="33">
         <v>120</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="33">
         <f t="shared" ref="AD5:AD6" si="1">U5*$N$3</f>
         <v>9504</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <v>1</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="33">
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
@@ -7726,79 +7729,79 @@
       <c r="L6" s="33">
         <v>0</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="33">
         <f>I6</f>
         <v>20000</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="33">
         <f>ROUND((M6*J6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="33">
         <f>I6-N6</f>
         <v>20000</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="33">
         <f>ROUND((O6*K6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="33">
         <f>ROUND(O6-P6,2)</f>
         <v>20000</v>
       </c>
-      <c r="R6" s="29">
+      <c r="R6" s="33">
         <f>ROUND((Q6*L6)/100,2)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="31">
+      <c r="S6" s="33">
         <f>N6+P6+R6</f>
         <v>0</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="33">
         <f>S6/G6</f>
         <v>0</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="33">
         <f>(I6-S6)</f>
         <v>20000</v>
       </c>
-      <c r="V6" s="29" t="s">
+      <c r="V6" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W6" s="30">
         <v>0.05</v>
       </c>
-      <c r="X6" s="29">
+      <c r="X6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="29">
+      <c r="Y6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="29">
+      <c r="Z6" s="33">
         <f>ROUND(IF($D$3=2,((U6*W6)),0),2)</f>
         <v>1000</v>
       </c>
-      <c r="AA6" s="29">
+      <c r="AA6" s="33">
         <f>X6+Y6+Z6</f>
         <v>1000</v>
       </c>
-      <c r="AB6" s="29">
+      <c r="AB6" s="33">
         <f t="shared" si="0"/>
         <v>21000</v>
       </c>
-      <c r="AC6" s="29">
+      <c r="AC6" s="33">
         <v>120</v>
       </c>
-      <c r="AD6" s="29">
+      <c r="AD6" s="33">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="AE6" s="32">
+      <c r="AE6" s="33">
         <v>3</v>
       </c>
-      <c r="AF6" s="32">
+      <c r="AF6" s="33">
         <f>ROUND(G6/AE6,3)</f>
         <v>3.3330000000000002</v>
       </c>
@@ -7810,7 +7813,7 @@
       </c>
       <c r="AI6" s="29">
         <f>ROUND((AG6-AF6),3)</f>
-        <v>1375.002</v>
+        <v>-3.3330000000000002</v>
       </c>
       <c r="AJ6" s="27" t="s">
         <v>59</v>
@@ -8246,79 +8249,79 @@
       <c r="L5" s="33">
         <v>10</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="33">
         <f>I5</f>
         <v>15000</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="33">
         <f>ROUND((M5*J5)/100,2)</f>
         <v>1500</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <f>I5-N5</f>
         <v>13500</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="33">
         <f>ROUND((O5*K5)/100,2)</f>
         <v>1350</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="33">
         <f>ROUND(O5-P5,2)</f>
         <v>12150</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="33">
         <f>ROUND((Q5*L5)/100,2)</f>
         <v>1215</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="33">
         <f>ROUND(N5+P5+R5,2)</f>
         <v>4065</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="33">
         <f>S5/G5</f>
         <v>406.5</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="33">
         <f>(I5-S5)</f>
         <v>10935</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="V5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W5" s="30">
         <v>0.12</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>656.1</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="33">
         <f>IF($D$3=1,ROUND(((U5*W5)/2),2),0)</f>
         <v>656.1</v>
       </c>
-      <c r="Z5" s="29">
+      <c r="Z5" s="33">
         <f>IF($D$3=2,ROUND(((U5*W5)),2),0)</f>
         <v>0</v>
       </c>
-      <c r="AA5" s="29">
+      <c r="AA5" s="33">
         <f>X5+Y5+Z5</f>
         <v>1312.2</v>
       </c>
-      <c r="AB5" s="29">
+      <c r="AB5" s="33">
         <f t="shared" ref="AB5:AB6" si="0">U5+AA5</f>
         <v>12247.2</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="33">
         <v>120</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="33">
         <f t="shared" ref="AD5:AD6" si="1">U5*$N$3</f>
         <v>10935</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <v>1</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="33">
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
@@ -8384,79 +8387,79 @@
       <c r="L6" s="33">
         <v>10</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="33">
         <f>I6</f>
         <v>20000</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="33">
         <f>ROUND((M6*J6)/100,2)</f>
         <v>2000</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="33">
         <f>I6-N6</f>
         <v>18000</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="33">
         <f>ROUND((O6*K6)/100,2)</f>
         <v>1800</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="33">
         <f>ROUND(O6-P6,2)</f>
         <v>16200</v>
       </c>
-      <c r="R6" s="29">
+      <c r="R6" s="33">
         <f>ROUND((Q6*L6)/100,2)</f>
         <v>1620</v>
       </c>
-      <c r="S6" s="31">
+      <c r="S6" s="33">
         <f>ROUND(N6+P6+R6,2)</f>
         <v>5420</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="33">
         <f>S6/G6</f>
         <v>542</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="33">
         <f>(I6-S6)</f>
         <v>14580</v>
       </c>
-      <c r="V6" s="29" t="s">
+      <c r="V6" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W6" s="30">
         <v>0.05</v>
       </c>
-      <c r="X6" s="29">
+      <c r="X6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>364.5</v>
       </c>
-      <c r="Y6" s="29">
+      <c r="Y6" s="33">
         <f>IF($D$3=1,ROUND(((U6*W6)/2),2),0)</f>
         <v>364.5</v>
       </c>
-      <c r="Z6" s="29">
+      <c r="Z6" s="33">
         <f>IF($D$3=2,ROUND(((U6*W6)),2),0)</f>
         <v>0</v>
       </c>
-      <c r="AA6" s="29">
+      <c r="AA6" s="33">
         <f>X6+Y6+Z6</f>
         <v>729</v>
       </c>
-      <c r="AB6" s="29">
+      <c r="AB6" s="33">
         <f t="shared" si="0"/>
         <v>15309</v>
       </c>
-      <c r="AC6" s="29">
+      <c r="AC6" s="33">
         <v>120</v>
       </c>
-      <c r="AD6" s="29">
+      <c r="AD6" s="33">
         <f t="shared" si="1"/>
         <v>14580</v>
       </c>
-      <c r="AE6" s="32">
+      <c r="AE6" s="33">
         <v>3</v>
       </c>
-      <c r="AF6" s="32">
+      <c r="AF6" s="33">
         <f>ROUND(G6/AE6,3)</f>
         <v>3.3330000000000002</v>
       </c>
@@ -8468,7 +8471,7 @@
       </c>
       <c r="AI6" s="29">
         <f>ROUND((AG6-AF6),3)</f>
-        <v>-3.3330000000000002</v>
+        <v>1371.6690000000001</v>
       </c>
       <c r="AJ6" s="27" t="s">
         <v>50</v>
@@ -8904,75 +8907,75 @@
       <c r="L5" s="33">
         <v>10</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="33">
         <f>I5</f>
         <v>15000</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="33">
         <f>ROUND((M5*J5)/100,2)</f>
         <v>1500</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <f>I5-N5</f>
         <v>13500</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="33">
         <f>ROUND((O5*K5)/100,2)</f>
         <v>1350</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="33">
         <f>ROUND(O5-P5,2)</f>
         <v>12150</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="33">
         <f>ROUND((Q5*L5)/100,2)</f>
         <v>1215</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="33">
         <f>ROUND(N5+P5+R5,2)</f>
         <v>4065</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="33">
         <f>S5/G5</f>
         <v>406.5</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="33">
         <f>(I5-S5)</f>
         <v>10935</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="V5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W5" s="30">
         <v>0.12</v>
       </c>
-      <c r="X5" s="29">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="29">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="29">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="29">
+      <c r="X5" s="33">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="33">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="33">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="33">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="33">
         <f>U5+AA5</f>
         <v>10935</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="33">
         <v>120</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="33">
         <f t="shared" ref="AD5:AD6" si="0">U5*$N$3</f>
         <v>10935</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <v>1</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="33">
         <f t="shared" ref="AF5" si="1">G5/AE5</f>
         <v>10</v>
       </c>
@@ -9038,75 +9041,75 @@
       <c r="L6" s="33">
         <v>10</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="33">
         <f>I6</f>
         <v>20000</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="33">
         <f>ROUND((M6*J6)/100,2)</f>
         <v>2000</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="33">
         <f>I6-N6</f>
         <v>18000</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="33">
         <f>ROUND((O6*K6)/100,2)</f>
         <v>1800</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="33">
         <f>ROUND(O6-P6,2)</f>
         <v>16200</v>
       </c>
-      <c r="R6" s="29">
+      <c r="R6" s="33">
         <f>ROUND((Q6*L6)/100,2)</f>
         <v>1620</v>
       </c>
-      <c r="S6" s="31">
+      <c r="S6" s="33">
         <f>ROUND(N6+P6+R6,2)</f>
         <v>5420</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="33">
         <f>S6/G6</f>
         <v>542</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="33">
         <f>(I6-S6)</f>
         <v>14580</v>
       </c>
-      <c r="V6" s="29" t="s">
+      <c r="V6" s="33" t="s">
         <v>23</v>
       </c>
       <c r="W6" s="30">
         <v>0.05</v>
       </c>
-      <c r="X6" s="29">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="29">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="29">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="29">
+      <c r="X6" s="33">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="33">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="33">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="33">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="33">
         <f t="shared" ref="AB6" si="2">U6+AA6</f>
         <v>14580</v>
       </c>
-      <c r="AC6" s="29">
+      <c r="AC6" s="33">
         <v>120</v>
       </c>
-      <c r="AD6" s="29">
+      <c r="AD6" s="33">
         <f t="shared" si="0"/>
         <v>14580</v>
       </c>
-      <c r="AE6" s="32">
+      <c r="AE6" s="33">
         <v>3</v>
       </c>
-      <c r="AF6" s="32">
+      <c r="AF6" s="33">
         <f>ROUND(G6/AE6,3)</f>
         <v>3.3330000000000002</v>
       </c>
@@ -9118,7 +9121,7 @@
       </c>
       <c r="AI6" s="29">
         <f>ROUND((AG6-AF6),3)</f>
-        <v>1375.002</v>
+        <v>1371.6690000000001</v>
       </c>
       <c r="AJ6" s="27" t="s">
         <v>50</v>

--- a/testdata/QA Scenario - Sales STD PRICE.xlsx
+++ b/testdata/QA Scenario - Sales STD PRICE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="40" activeTab="42"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="40" activeTab="41"/>
   </bookViews>
   <sheets>
     <sheet name="SO Domestic PL (S&amp;D)" sheetId="25" r:id="rId1"/>

--- a/testdata/QA Scenario - Sales STD PRICE.xlsx
+++ b/testdata/QA Scenario - Sales STD PRICE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="44" activeTab="46"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="43" activeTab="45"/>
   </bookViews>
   <sheets>
     <sheet name="SO Domestic PL (S&amp;D)" sheetId="25" r:id="rId1"/>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3921" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3919" uniqueCount="192">
   <si>
     <t>Item</t>
   </si>
@@ -19540,7 +19540,7 @@
     <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
@@ -19559,10 +19559,11 @@
     <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="67" width="9.140625" style="1"/>
-    <col min="68" max="68" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="9.140625" style="1"/>
+    <col min="67" max="67" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="9.140625" style="1"/>
     <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -20093,11 +20094,11 @@
         <v>10</v>
       </c>
       <c r="AS5" s="27">
-        <v>2678</v>
+        <v>1234</v>
       </c>
       <c r="AT5" s="27">
         <f>AR5*AS5</f>
-        <v>26780</v>
+        <v>12340</v>
       </c>
       <c r="AU5" s="27">
         <v>1</v>
@@ -20110,39 +20111,39 @@
       </c>
       <c r="AX5" s="27">
         <f>AT5</f>
-        <v>26780</v>
+        <v>12340</v>
       </c>
       <c r="AY5" s="27">
         <f>ROUND((AX5*AU5)/100,2)</f>
-        <v>267.8</v>
+        <v>123.4</v>
       </c>
       <c r="AZ5" s="27">
         <f>AT5-AY5</f>
-        <v>26512.2</v>
+        <v>12216.6</v>
       </c>
       <c r="BA5" s="27">
         <f>ROUND((AZ5*AV5)/100,2)</f>
-        <v>530.24</v>
+        <v>244.33</v>
       </c>
       <c r="BB5" s="27">
         <f>ROUND(AZ5-BA5,2)</f>
-        <v>25981.96</v>
+        <v>11972.27</v>
       </c>
       <c r="BC5" s="27">
         <f>ROUND((BB5*AW5)/100,2)</f>
-        <v>1039.28</v>
+        <v>478.89</v>
       </c>
       <c r="BD5" s="27">
         <f>AY5+BA5+BC5</f>
-        <v>1837.32</v>
+        <v>846.62</v>
       </c>
       <c r="BE5" s="27">
         <f>ROUND(BD5/AR5,2)</f>
-        <v>183.73</v>
+        <v>84.66</v>
       </c>
       <c r="BF5" s="27">
         <f>(AT5-BD5)</f>
-        <v>24942.68</v>
+        <v>11493.38</v>
       </c>
       <c r="BG5" s="27" t="s">
         <v>173</v>
@@ -20152,7 +20153,7 @@
       </c>
       <c r="BI5" s="27">
         <f>IF(OR($D$3=1,$D$3=4),ROUND((BF5*BH5)/2,2),0)</f>
-        <v>1496.56</v>
+        <v>689.6</v>
       </c>
       <c r="BJ5" s="27">
         <f>IF($D$3=1,ROUND(((BF5*BH5)/2),2),0)</f>
@@ -20164,7 +20165,7 @@
       </c>
       <c r="BL5" s="27">
         <f>IF($D$3=4,ROUND(((BF5*BH5)/2),2),0)</f>
-        <v>1496.56</v>
+        <v>689.6</v>
       </c>
       <c r="BM5" s="30">
         <v>0.06</v>
@@ -20175,18 +20176,18 @@
       </c>
       <c r="BO5" s="27">
         <f>BI5+BJ5+BK5+BL5+BN5</f>
-        <v>2993.12</v>
+        <v>1379.2</v>
       </c>
       <c r="BP5" s="27">
         <f t="shared" ref="BP5:BP6" si="0">BF5+BO5</f>
-        <v>27935.8</v>
+        <v>12872.58</v>
       </c>
       <c r="BQ5" s="27">
         <v>120</v>
       </c>
       <c r="BR5" s="27">
         <f>BF5*$N$3</f>
-        <v>24942.68</v>
+        <v>11493.38</v>
       </c>
       <c r="BS5" s="27" t="s">
         <v>101</v>
@@ -20373,11 +20374,11 @@
         <v>20</v>
       </c>
       <c r="AS6" s="27">
-        <v>4256</v>
+        <v>3214</v>
       </c>
       <c r="AT6" s="27">
         <f>AR6*AS6</f>
-        <v>85120</v>
+        <v>64280</v>
       </c>
       <c r="AU6" s="27">
         <v>2</v>
@@ -20390,39 +20391,39 @@
       </c>
       <c r="AX6" s="27">
         <f>AT6</f>
-        <v>85120</v>
+        <v>64280</v>
       </c>
       <c r="AY6" s="27">
         <f>ROUND((AX6*AU6)/100,2)</f>
-        <v>1702.4</v>
+        <v>1285.5999999999999</v>
       </c>
       <c r="AZ6" s="27">
         <f>AT6-AY6</f>
-        <v>83417.600000000006</v>
+        <v>62994.400000000001</v>
       </c>
       <c r="BA6" s="27">
         <f>ROUND((AZ6*AV6)/100,2)</f>
-        <v>5839.23</v>
+        <v>4409.6099999999997</v>
       </c>
       <c r="BB6" s="27">
         <f>ROUND(AZ6-BA6,2)</f>
-        <v>77578.37</v>
+        <v>58584.79</v>
       </c>
       <c r="BC6" s="27">
         <f>ROUND((BB6*AW6)/100,2)</f>
-        <v>6982.05</v>
+        <v>5272.63</v>
       </c>
       <c r="BD6" s="27">
         <f>AY6+BA6+BC6</f>
-        <v>14523.68</v>
+        <v>10967.84</v>
       </c>
       <c r="BE6" s="27">
         <f>ROUND(BD6/AR6,2)</f>
-        <v>726.18</v>
+        <v>548.39</v>
       </c>
       <c r="BF6" s="27">
         <f>(AT6-BD6)</f>
-        <v>70596.320000000007</v>
+        <v>53312.160000000003</v>
       </c>
       <c r="BG6" s="27" t="s">
         <v>191</v>
@@ -20432,7 +20433,7 @@
       </c>
       <c r="BI6" s="27">
         <f>IF(OR($D$3=1,$D$3=4),ROUND((BF6*BH6)/2,2),0)</f>
-        <v>1764.91</v>
+        <v>1332.8</v>
       </c>
       <c r="BJ6" s="27">
         <f>IF($D$3=1,ROUND(((BF6*BH6)/2),2),0)</f>
@@ -20444,7 +20445,7 @@
       </c>
       <c r="BL6" s="27">
         <f>IF($D$3=4,ROUND(((BF6*BH6)/2),2),0)</f>
-        <v>1764.91</v>
+        <v>1332.8</v>
       </c>
       <c r="BM6" s="30">
         <v>0.06</v>
@@ -20455,18 +20456,18 @@
       </c>
       <c r="BO6" s="27">
         <f>BI6+BJ6+BK6+BL6+BN6</f>
-        <v>3529.82</v>
+        <v>2665.6</v>
       </c>
       <c r="BP6" s="27">
         <f t="shared" si="0"/>
-        <v>74126.140000000014</v>
+        <v>55977.760000000002</v>
       </c>
       <c r="BQ6" s="27">
         <v>120</v>
       </c>
       <c r="BR6" s="27">
         <f t="shared" ref="BR6" si="1">BF6*$N$3</f>
-        <v>70596.320000000007</v>
+        <v>53312.160000000003</v>
       </c>
       <c r="BS6" s="27" t="s">
         <v>101</v>
@@ -20663,15 +20664,15 @@
         <f>(AT7-BD7)</f>
         <v>234714.69</v>
       </c>
-      <c r="BG7" s="27" t="s">
-        <v>191</v>
+      <c r="BG7" s="27">
+        <v>88363222</v>
       </c>
       <c r="BH7" s="30">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="BI7" s="27">
         <f>IF(OR($D$3=1,$D$3=4),ROUND((BF7*BH7)/2,2),0)</f>
-        <v>5867.87</v>
+        <v>21124.32</v>
       </c>
       <c r="BJ7" s="27">
         <f>IF($D$3=1,ROUND(((BF7*BH7)/2),2),0)</f>
@@ -20683,7 +20684,7 @@
       </c>
       <c r="BL7" s="27">
         <f>IF($D$3=4,ROUND(((BF7*BH7)/2),2),0)</f>
-        <v>5867.87</v>
+        <v>21124.32</v>
       </c>
       <c r="BM7" s="30">
         <v>0.06</v>
@@ -20694,11 +20695,11 @@
       </c>
       <c r="BO7" s="27">
         <f>BI7+BJ7+BK7+BL7+BN7</f>
-        <v>11735.74</v>
+        <v>42248.639999999999</v>
       </c>
       <c r="BP7" s="27">
         <f t="shared" ref="BP7" si="2">BF7+BO7</f>
-        <v>246450.43</v>
+        <v>276963.33</v>
       </c>
       <c r="BQ7" s="27">
         <v>120</v>
@@ -20787,7 +20788,7 @@
       <c r="BC8" s="15"/>
       <c r="BD8" s="15">
         <f>SUM(BD5:BD7)</f>
-        <v>86706.31</v>
+        <v>82159.77</v>
       </c>
       <c r="BE8" s="15"/>
       <c r="BF8" s="13"/>
@@ -20804,14 +20805,14 @@
       <c r="BO8" s="15"/>
       <c r="BP8" s="79">
         <f>SUM(BP5:BP7)</f>
-        <v>348512.37</v>
+        <v>345813.67000000004</v>
       </c>
       <c r="BQ8" s="15" t="s">
         <v>40</v>
       </c>
       <c r="BR8" s="79">
         <f>SUM(BR5:BR7)</f>
-        <v>330253.69</v>
+        <v>299520.23</v>
       </c>
     </row>
     <row r="9" spans="1:73" ht="14.25" customHeight="1">
@@ -22295,7 +22296,7 @@
     <col min="56" max="56" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -28812,7 +28813,9 @@
     <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
     <col min="38" max="42" width="9.140625" style="1"/>
     <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="49" width="9.140625" style="1"/>
+    <col min="44" max="45" width="9.140625" style="1"/>
+    <col min="46" max="46" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="49" width="9.140625" style="1"/>
     <col min="50" max="50" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="9.140625" style="1"/>
     <col min="52" max="52" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -29241,7 +29244,7 @@
         <v>13546.05</v>
       </c>
       <c r="V5" s="27" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="W5" s="30">
         <v>0.12</v>
@@ -29373,7 +29376,7 @@
         <v>9761.4</v>
       </c>
       <c r="BG5" s="27" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="BH5" s="30">
         <v>0.12</v>
@@ -29501,7 +29504,7 @@
         <v>16079.7</v>
       </c>
       <c r="V6" s="27" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="W6" s="30">
         <v>0.05</v>
@@ -29578,14 +29581,14 @@
         <v>101</v>
       </c>
       <c r="AR6" s="27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AS6" s="27">
         <v>2000</v>
       </c>
       <c r="AT6" s="27">
         <f>AR6*AS6</f>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="AU6" s="27">
         <v>15</v>
@@ -29598,31 +29601,31 @@
       </c>
       <c r="AX6" s="27">
         <f>AT6</f>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="AY6" s="27">
         <f>ROUND((AX6*AU6)/100,2)</f>
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AZ6" s="27">
         <f>AT6-AY6</f>
-        <v>34000</v>
+        <v>17000</v>
       </c>
       <c r="BA6" s="27">
         <f>ROUND((AZ6*AV6)/100,2)</f>
-        <v>5780</v>
+        <v>2890</v>
       </c>
       <c r="BB6" s="27">
         <f>ROUND(AZ6-BA6,2)</f>
-        <v>28220</v>
+        <v>14110</v>
       </c>
       <c r="BC6" s="27">
         <f>ROUND((BB6*AW6)/100,2)</f>
-        <v>5361.8</v>
+        <v>2680.9</v>
       </c>
       <c r="BD6" s="27">
         <f>ROUND(AY6+BA6+BC6,2)</f>
-        <v>17141.8</v>
+        <v>8570.9</v>
       </c>
       <c r="BE6" s="27">
         <f>ROUND(BD6/AR6,2)</f>
@@ -29630,21 +29633,21 @@
       </c>
       <c r="BF6" s="27">
         <f>(AT6-BD6)</f>
-        <v>22858.2</v>
+        <v>11429.1</v>
       </c>
       <c r="BG6" s="27" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="BH6" s="30">
         <v>0.05</v>
       </c>
       <c r="BI6" s="27">
         <f>IF(OR($D$3=1,$D$3=4),ROUND((BF6*BH6)/2,2),0)</f>
-        <v>571.46</v>
+        <v>285.73</v>
       </c>
       <c r="BJ6" s="27">
         <f>IF($D$3=1,ROUND(((BF6*BH6)/2),2),0)</f>
-        <v>571.46</v>
+        <v>285.73</v>
       </c>
       <c r="BK6" s="27">
         <f>IF($D$3=2,ROUND(((BF6*BH6)),2),0)</f>
@@ -29663,18 +29666,18 @@
       </c>
       <c r="BO6" s="27">
         <f>BI6+BJ6+BK6+BL6+BN6</f>
-        <v>1142.92</v>
+        <v>571.46</v>
       </c>
       <c r="BP6" s="27">
         <f t="shared" si="3"/>
-        <v>24001.120000000003</v>
+        <v>12000.560000000001</v>
       </c>
       <c r="BQ6" s="27">
         <v>120</v>
       </c>
       <c r="BR6" s="27">
         <f t="shared" si="4"/>
-        <v>22858.2</v>
+        <v>11429.1</v>
       </c>
       <c r="BS6" s="27" t="s">
         <v>61</v>
@@ -29767,7 +29770,7 @@
       <c r="BO7" s="15"/>
       <c r="BP7" s="79">
         <f>SUM(BP5:BP6)</f>
-        <v>34933.880000000005</v>
+        <v>22933.32</v>
       </c>
       <c r="BQ7" s="15" t="s">
         <v>40</v>
@@ -34906,7 +34909,7 @@
         <v>39381.300000000003</v>
       </c>
       <c r="BM5" s="27" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="BN5" s="27" t="s">
         <v>159</v>
@@ -35150,7 +35153,7 @@
         <v>93366</v>
       </c>
       <c r="BM6" s="27" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="BN6" s="27" t="s">
         <v>159</v>
@@ -35296,7 +35299,7 @@
     <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -36446,7 +36449,7 @@
     <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
@@ -36466,7 +36469,12 @@
     <col min="50" max="50" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="9.140625" style="1"/>
     <col min="52" max="52" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="70" width="9.140625" style="1"/>
+    <col min="53" max="58" width="9.140625" style="1"/>
+    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="67" width="9.140625" style="1"/>
+    <col min="68" max="68" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="9.140625" style="1"/>
     <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="72" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -36893,7 +36901,7 @@
         <v>13546.05</v>
       </c>
       <c r="V5" s="27" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="W5" s="30">
         <v>0.12</v>
@@ -36970,14 +36978,14 @@
         <v>101</v>
       </c>
       <c r="AR5" s="27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AS5" s="27">
         <v>1500</v>
       </c>
       <c r="AT5" s="27">
         <f>AR5*AS5</f>
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="AU5" s="27">
         <v>2</v>
@@ -36990,31 +36998,31 @@
       </c>
       <c r="AX5" s="27">
         <f>AT5</f>
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="AY5" s="27">
         <f>ROUND((AX5*AU5)/100,2)</f>
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="AZ5" s="27">
         <f>AT5-AY5</f>
-        <v>29400</v>
+        <v>14700</v>
       </c>
       <c r="BA5" s="27">
         <f>ROUND((AZ5*AV5)/100,2)</f>
-        <v>882</v>
+        <v>441</v>
       </c>
       <c r="BB5" s="27">
         <f>ROUND(AZ5-BA5,2)</f>
-        <v>28518</v>
+        <v>14259</v>
       </c>
       <c r="BC5" s="27">
         <f>ROUND((BB5*AW5)/100,2)</f>
-        <v>1425.9</v>
+        <v>712.95</v>
       </c>
       <c r="BD5" s="27">
         <f>ROUND(AY5+BA5+BC5,2)</f>
-        <v>2907.9</v>
+        <v>1453.95</v>
       </c>
       <c r="BE5" s="27">
         <f>ROUND(BD5/AR5,2)</f>
@@ -37022,21 +37030,21 @@
       </c>
       <c r="BF5" s="27">
         <f>(AT5-BD5)</f>
-        <v>27092.1</v>
+        <v>13546.05</v>
       </c>
       <c r="BG5" s="27" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="BH5" s="30">
         <v>0.12</v>
       </c>
       <c r="BI5" s="27">
         <f>IF(OR($D$3=1,$D$3=4),ROUND((BF5*BH5)/2,2),0)</f>
-        <v>1625.53</v>
+        <v>812.76</v>
       </c>
       <c r="BJ5" s="27">
         <f>IF($D$3=1,ROUND(((BF5*BH5)/2),2),0)</f>
-        <v>1625.53</v>
+        <v>812.76</v>
       </c>
       <c r="BK5" s="27">
         <f>IF($D$3=2,ROUND(((BF5*BH5)),2),0)</f>
@@ -37055,18 +37063,18 @@
       </c>
       <c r="BO5" s="27">
         <f>BI5+BJ5+BK5+BL5+BN5</f>
-        <v>3251.06</v>
+        <v>1625.52</v>
       </c>
       <c r="BP5" s="27">
         <f t="shared" ref="BP5:BP7" si="3">BF5+BO5</f>
-        <v>30343.16</v>
+        <v>15171.57</v>
       </c>
       <c r="BQ5" s="27">
         <v>120</v>
       </c>
       <c r="BR5" s="27">
         <f t="shared" ref="BR5:BR7" si="4">BF5*$N$3</f>
-        <v>27092.1</v>
+        <v>13546.05</v>
       </c>
       <c r="BS5" s="27" t="s">
         <v>61</v>
@@ -37153,7 +37161,7 @@
         <v>16079.7</v>
       </c>
       <c r="V6" s="27" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="W6" s="30">
         <v>0.05</v>
@@ -37230,14 +37238,14 @@
         <v>101</v>
       </c>
       <c r="AR6" s="27">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AS6" s="27">
         <v>2000</v>
       </c>
       <c r="AT6" s="27">
         <f>AR6*AS6</f>
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="AU6" s="27">
         <v>5</v>
@@ -37250,31 +37258,31 @@
       </c>
       <c r="AX6" s="27">
         <f>AT6</f>
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="AY6" s="27">
         <f>ROUND((AX6*AU6)/100,2)</f>
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="AZ6" s="27">
         <f>AT6-AY6</f>
-        <v>57000</v>
+        <v>19000</v>
       </c>
       <c r="BA6" s="27">
         <f>ROUND((AZ6*AV6)/100,2)</f>
-        <v>3990</v>
+        <v>1330</v>
       </c>
       <c r="BB6" s="27">
         <f>ROUND(AZ6-BA6,2)</f>
-        <v>53010</v>
+        <v>17670</v>
       </c>
       <c r="BC6" s="27">
         <f>ROUND((BB6*AW6)/100,2)</f>
-        <v>4770.8999999999996</v>
+        <v>1590.3</v>
       </c>
       <c r="BD6" s="27">
         <f>ROUND(AY6+BA6+BC6,2)</f>
-        <v>11760.9</v>
+        <v>3920.3</v>
       </c>
       <c r="BE6" s="27">
         <f>ROUND(BD6/AR6,2)</f>
@@ -37282,21 +37290,21 @@
       </c>
       <c r="BF6" s="27">
         <f>(AT6-BD6)</f>
-        <v>48239.1</v>
+        <v>16079.7</v>
       </c>
       <c r="BG6" s="27" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="BH6" s="30">
         <v>0.05</v>
       </c>
       <c r="BI6" s="27">
         <f>IF(OR($D$3=1,$D$3=4),ROUND((BF6*BH6)/2,2),0)</f>
-        <v>1205.98</v>
+        <v>401.99</v>
       </c>
       <c r="BJ6" s="27">
         <f>IF($D$3=1,ROUND(((BF6*BH6)/2),2),0)</f>
-        <v>1205.98</v>
+        <v>401.99</v>
       </c>
       <c r="BK6" s="27">
         <f>IF($D$3=2,ROUND(((BF6*BH6)),2),0)</f>
@@ -37315,18 +37323,18 @@
       </c>
       <c r="BO6" s="27">
         <f>BI6+BJ6+BK6+BL6+BN6</f>
-        <v>2411.96</v>
+        <v>803.98</v>
       </c>
       <c r="BP6" s="27">
         <f t="shared" si="3"/>
-        <v>50651.06</v>
+        <v>16883.68</v>
       </c>
       <c r="BQ6" s="27">
         <v>120</v>
       </c>
       <c r="BR6" s="27">
         <f t="shared" si="4"/>
-        <v>48239.1</v>
+        <v>16079.7</v>
       </c>
       <c r="BS6" s="27" t="s">
         <v>61</v>
@@ -37402,9 +37410,7 @@
       <c r="U7" s="31">
         <v>0</v>
       </c>
-      <c r="V7" s="31">
-        <v>0</v>
-      </c>
+      <c r="V7" s="27"/>
       <c r="W7" s="31">
         <v>0</v>
       </c>
@@ -37523,19 +37529,19 @@
         <f>(AT7-BD7)</f>
         <v>234714.69</v>
       </c>
-      <c r="BG7" s="27" t="s">
-        <v>191</v>
+      <c r="BG7" s="27">
+        <v>88363222</v>
       </c>
       <c r="BH7" s="30">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="BI7" s="27">
         <f>IF(OR($D$3=1,$D$3=4),ROUND((BF7*BH7)/2,2),0)</f>
-        <v>5867.87</v>
+        <v>21124.32</v>
       </c>
       <c r="BJ7" s="27">
         <f>IF($D$3=1,ROUND(((BF7*BH7)/2),2),0)</f>
-        <v>5867.87</v>
+        <v>21124.32</v>
       </c>
       <c r="BK7" s="27">
         <f>IF($D$3=2,ROUND(((BF7*BH7)),2),0)</f>
@@ -37554,11 +37560,11 @@
       </c>
       <c r="BO7" s="27">
         <f>BI7+BJ7+BK7+BL7+BN7</f>
-        <v>11735.74</v>
+        <v>42248.639999999999</v>
       </c>
       <c r="BP7" s="27">
         <f t="shared" si="3"/>
-        <v>246450.43</v>
+        <v>276963.33</v>
       </c>
       <c r="BQ7" s="27">
         <v>120</v>
@@ -37657,15 +37663,15 @@
       <c r="BN8" s="15"/>
       <c r="BO8" s="15"/>
       <c r="BP8" s="79">
-        <f>SUM(BP5:BP6)</f>
-        <v>80994.22</v>
+        <f>SUM(BP5:BP7)</f>
+        <v>309018.58</v>
       </c>
       <c r="BQ8" s="15" t="s">
         <v>40</v>
       </c>
       <c r="BR8" s="79">
         <f>BR5</f>
-        <v>27092.1</v>
+        <v>13546.05</v>
       </c>
     </row>
     <row r="9" spans="1:73" ht="14.25" customHeight="1">

--- a/testdata/QA Scenario - Sales STD PRICE.xlsx
+++ b/testdata/QA Scenario - Sales STD PRICE.xlsx
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3950" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="199">
   <si>
     <t>Scenario  : Local Sales - Stock UOM and Sales UOM (Similar)   DOC NO :  SORD-2425-00089</t>
   </si>
@@ -2091,43 +2091,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="32.5727272727273" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="38.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="32.5727272727273"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="38.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -2409,14 +2409,14 @@
       <c r="G5" s="9">
         <v>44</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" t="s" s="16">
         <v>51</v>
       </c>
       <c r="I5" s="9">
         <f>ROUND(G5*H5,2)</f>
         <v>73700</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" t="s" s="16">
         <v>52</v>
       </c>
       <c r="K5" s="9">
@@ -2561,14 +2561,14 @@
       <c r="G6" s="9">
         <v>53</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" t="s" s="16">
         <v>61</v>
       </c>
       <c r="I6" s="9">
         <f>ROUND(G6*H6,2)</f>
         <v>171879</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" t="s" s="16">
         <v>62</v>
       </c>
       <c r="K6" s="9">
@@ -2796,41 +2796,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -3112,14 +3112,14 @@
       <c r="G5" s="9">
         <v>10</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" t="s" s="16">
         <v>93</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
         <v>21800</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" t="s" s="16">
         <v>62</v>
       </c>
       <c r="K5" s="9">
@@ -3264,14 +3264,14 @@
       <c r="G6" s="9">
         <v>10</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" t="s" s="16">
         <v>94</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
         <v>31200</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" t="s" s="16">
         <v>95</v>
       </c>
       <c r="K6" s="9">
@@ -3499,41 +3499,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -4203,46 +4203,46 @@
   <dimension ref="A1:AR7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="44" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="45" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="41" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="45" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -4765,46 +4765,46 @@
   <dimension ref="A1:AR8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="44" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="45" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="41" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="45" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -5482,43 +5482,43 @@
   <dimension ref="A1:AR8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="29" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="30" max="30" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="31" max="31" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="32" max="32" width="16" style="16" customWidth="1"/>
-    <col min="33" max="33" width="12" style="16" customWidth="1"/>
-    <col min="34" max="34" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="35" max="35" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="36" max="37" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="38" max="38" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="39" max="39" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="40" max="40" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="29" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="30" max="30" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="31" max="31" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="32" max="32" customWidth="true" style="16" width="16.0"/>
+    <col min="33" max="33" customWidth="true" style="16" width="12.0"/>
+    <col min="34" max="34" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="36" max="37" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="38" max="38" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="39" max="39" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="40" max="40" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="41" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:37">
@@ -6207,14 +6207,14 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.42727272727273" customWidth="1"/>
-    <col min="2" max="2" width="28.7090909090909" customWidth="1"/>
-    <col min="3" max="3" width="5" customWidth="1"/>
-    <col min="4" max="4" width="28.7090909090909" customWidth="1"/>
-    <col min="5" max="5" width="10.8545454545455" customWidth="1"/>
-    <col min="6" max="6" width="10.1363636363636" customWidth="1"/>
-    <col min="7" max="7" width="17.8545454545455" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="6.42727272727273"/>
+    <col min="2" max="2" customWidth="true" width="28.7090909090909"/>
+    <col min="3" max="3" customWidth="true" width="5.0"/>
+    <col min="4" max="4" customWidth="true" width="28.7090909090909"/>
+    <col min="5" max="5" customWidth="true" width="10.8545454545455"/>
+    <col min="6" max="6" customWidth="true" width="10.1363636363636"/>
+    <col min="7" max="7" customWidth="true" width="17.8545454545455"/>
+    <col min="8" max="8" customWidth="true" width="16.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -6244,19 +6244,19 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2">
+      <c r="A2" s="0">
         <f>'Case 1'!A5</f>
         <v>1</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" t="str" s="0">
         <f>'Case 1'!B5</f>
         <v>HK-FIFO-LOT-BATCH-10001(FG)</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <f>'Case 1'!C5</f>
         <v>0</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" t="str" s="0">
         <f>'Case 1'!D5</f>
         <v>HK-FIFO-LOT-BATCH-10001(FG)</v>
       </c>
@@ -6267,7 +6267,7 @@
         <f>'Case 1'!H5</f>
         <v>1234</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>98</v>
       </c>
       <c r="H2" s="78">
@@ -6276,19 +6276,19 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3">
+      <c r="A3" s="0">
         <f>'Case 1'!A6</f>
         <v>2</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" t="str" s="0">
         <f>'Case 1'!B6</f>
         <v>HK-FG-DISSIMILAR-10001</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <f>'Case 1'!C6</f>
         <v>0</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" t="str" s="0">
         <f>'Case 1'!D6</f>
         <v>HK-FG-DISSIMILAR-10001</v>
       </c>
@@ -6299,7 +6299,7 @@
         <f>'Case 1'!H6</f>
         <v>3214</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="0">
         <v>675</v>
       </c>
       <c r="H3" s="78">
@@ -6319,69 +6319,69 @@
   <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="57" max="57" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="16" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -7057,45 +7057,45 @@
   <dimension ref="A1:AR8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="31.7090909090909" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="31.7090909090909" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="31.7090909090909"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="31.7090909090909"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -7773,41 +7773,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -8476,41 +8476,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -9179,41 +9179,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -9495,14 +9495,14 @@
       <c r="G5" s="9">
         <v>5</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" t="s" s="16">
         <v>68</v>
       </c>
       <c r="I5" s="9">
         <f>ROUND(G5*H5,2)</f>
         <v>120</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" t="s" s="16">
         <v>52</v>
       </c>
       <c r="K5" s="9">
@@ -9646,14 +9646,14 @@
       <c r="G6" s="9">
         <v>89</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" t="s" s="16">
         <v>69</v>
       </c>
       <c r="I6" s="9">
         <f>ROUND(G6*H6,2)</f>
         <v>2670</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" t="s" s="16">
         <v>62</v>
       </c>
       <c r="K6" s="9">
@@ -9880,41 +9880,41 @@
   <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="14.5727272727273" style="48" customWidth="1"/>
-    <col min="36" max="36" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="37" max="37" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="14.5727272727273"/>
+    <col min="36" max="36" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="37" max="37" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -10430,43 +10430,43 @@
   <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="37" max="37" width="14.2818181818182" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="37" max="37" customWidth="true" style="16" width="14.2818181818182"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -10982,45 +10982,45 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="41" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -11687,41 +11687,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -12390,41 +12390,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -13096,43 +13096,43 @@
   <dimension ref="A1:AN8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -13758,45 +13758,45 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="12.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="12.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="41" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -14465,28 +14465,28 @@
   <dimension ref="A1:AQ26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.7090909090909" customWidth="1"/>
-    <col min="4" max="4" width="28.7090909090909" customWidth="1"/>
-    <col min="5" max="5" width="10.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="17.8545454545455" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11.8545454545455" customWidth="1"/>
-    <col min="13" max="13" width="15.1363636363636" customWidth="1"/>
-    <col min="14" max="14" width="11.7090909090909" customWidth="1"/>
-    <col min="15" max="15" width="13.2818181818182" customWidth="1"/>
-    <col min="16" max="16" width="15.1363636363636" customWidth="1"/>
-    <col min="17" max="17" width="22.5727272727273" customWidth="1"/>
-    <col min="18" max="18" width="10.5727272727273" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" customWidth="1"/>
-    <col min="21" max="21" width="10.7090909090909" customWidth="1"/>
-    <col min="28" max="28" width="10.7090909090909" customWidth="1"/>
-    <col min="29" max="29" width="14.8545454545455" customWidth="1"/>
-    <col min="30" max="30" width="10.7090909090909" customWidth="1"/>
-    <col min="31" max="31" width="13.5727272727273" customWidth="1"/>
-    <col min="32" max="32" width="15.5727272727273" customWidth="1"/>
-    <col min="35" max="35" width="10" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.7090909090909"/>
+    <col min="4" max="4" customWidth="true" width="28.7090909090909"/>
+    <col min="5" max="5" customWidth="true" width="10.4272727272727"/>
+    <col min="6" max="6" customWidth="true" width="17.8545454545455"/>
+    <col min="8" max="8" customWidth="true" width="11.0"/>
+    <col min="9" max="9" customWidth="true" width="11.8545454545455"/>
+    <col min="13" max="13" customWidth="true" width="15.1363636363636"/>
+    <col min="14" max="14" customWidth="true" width="11.7090909090909"/>
+    <col min="15" max="15" customWidth="true" width="13.2818181818182"/>
+    <col min="16" max="16" customWidth="true" width="15.1363636363636"/>
+    <col min="17" max="17" customWidth="true" width="22.5727272727273"/>
+    <col min="18" max="18" customWidth="true" width="10.5727272727273"/>
+    <col min="19" max="19" customWidth="true" width="11.0"/>
+    <col min="20" max="20" customWidth="true" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" width="10.7090909090909"/>
+    <col min="29" max="29" customWidth="true" width="14.8545454545455"/>
+    <col min="30" max="30" customWidth="true" width="10.7090909090909"/>
+    <col min="31" max="31" customWidth="true" width="13.5727272727273"/>
+    <col min="32" max="32" customWidth="true" width="15.5727272727273"/>
+    <col min="35" max="35" customWidth="true" width="10.0"/>
+    <col min="37" max="37" customWidth="true" width="12.7090909090909"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:39">
@@ -15737,76 +15737,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="32" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="33" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="34" max="34" width="13.5727272727273" style="27" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="16" style="16" customWidth="1"/>
-    <col min="46" max="46" width="16.8545454545455" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="18.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="18.4272727272727" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="15.8545454545455" style="16" customWidth="1"/>
-    <col min="57" max="57" width="22.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="15.5727272727273" style="16" customWidth="1"/>
-    <col min="59" max="59" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="13" style="16" customWidth="1"/>
-    <col min="65" max="65" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="66" max="66" width="16.2818181818182" style="16" customWidth="1"/>
-    <col min="67" max="67" width="14" style="16" customWidth="1"/>
-    <col min="68" max="68" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="69" max="69" width="15" style="16" customWidth="1"/>
-    <col min="70" max="70" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="71" max="71" width="11" style="16" customWidth="1"/>
-    <col min="72" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="33" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="34" max="34" customWidth="true" style="27" width="13.5727272727273"/>
+    <col min="35" max="35" customWidth="true" style="48" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="16.0"/>
+    <col min="46" max="46" customWidth="true" style="16" width="16.8545454545455"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="18.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="18.4272727272727"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="15.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="16" width="22.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="15.5727272727273"/>
+    <col min="59" max="59" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="13.0"/>
+    <col min="65" max="65" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="66" max="66" customWidth="true" style="16" width="16.2818181818182"/>
+    <col min="67" max="67" customWidth="true" style="16" width="14.0"/>
+    <col min="68" max="68" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="69" max="69" customWidth="true" style="16" width="15.0"/>
+    <col min="70" max="70" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="71" max="71" customWidth="true" style="16" width="11.0"/>
+    <col min="72" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -16850,76 +16850,76 @@
   <dimension ref="A1:BS17"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="32" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="33" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="34" max="34" width="13.5727272727273" style="27" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="16" style="16" customWidth="1"/>
-    <col min="46" max="46" width="16.8545454545455" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="18.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="18.4272727272727" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="15.8545454545455" style="16" customWidth="1"/>
-    <col min="57" max="57" width="22.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="15.5727272727273" style="16" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="13" style="16" customWidth="1"/>
-    <col min="65" max="65" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="66" max="66" width="16.2818181818182" style="16" customWidth="1"/>
-    <col min="67" max="67" width="14" style="16" customWidth="1"/>
-    <col min="68" max="68" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="69" max="69" width="15" style="16" customWidth="1"/>
-    <col min="70" max="70" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="71" max="71" width="11" style="16" customWidth="1"/>
-    <col min="72" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="33" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="34" max="34" customWidth="true" style="27" width="13.5727272727273"/>
+    <col min="35" max="35" customWidth="true" style="48" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="16.0"/>
+    <col min="46" max="46" customWidth="true" style="16" width="16.8545454545455"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="18.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="18.4272727272727"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="15.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="16" width="22.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="15.5727272727273"/>
+    <col min="59" max="59" customWidth="true" style="16" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="13.0"/>
+    <col min="65" max="65" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="66" max="66" customWidth="true" style="16" width="16.2818181818182"/>
+    <col min="67" max="67" customWidth="true" style="16" width="14.0"/>
+    <col min="68" max="68" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="69" max="69" customWidth="true" style="16" width="15.0"/>
+    <col min="70" max="70" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="71" max="71" customWidth="true" style="16" width="11.0"/>
+    <col min="72" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -18142,41 +18142,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="32.5727272727273" style="16" customWidth="1"/>
-    <col min="3" max="3" width="5" style="16" customWidth="1"/>
-    <col min="4" max="4" width="38.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="32.5727272727273"/>
+    <col min="3" max="3" customWidth="true" style="16" width="5.0"/>
+    <col min="4" max="4" customWidth="true" style="16" width="38.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -18458,7 +18458,7 @@
       <c r="G5" s="9">
         <v>21</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" t="s" s="16">
         <v>71</v>
       </c>
       <c r="I5" s="9">
@@ -18610,7 +18610,7 @@
       <c r="G6" s="9">
         <v>35</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" t="s" s="16">
         <v>73</v>
       </c>
       <c r="I6" s="9">
@@ -18845,76 +18845,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="32" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="33" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="34" max="34" width="13.5727272727273" style="27" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="16" style="16" customWidth="1"/>
-    <col min="46" max="46" width="16.8545454545455" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="18.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="18.4272727272727" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="15.8545454545455" style="16" customWidth="1"/>
-    <col min="57" max="57" width="22.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="15.5727272727273" style="16" customWidth="1"/>
-    <col min="59" max="59" width="15" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="13" style="16" customWidth="1"/>
-    <col min="65" max="65" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="66" max="66" width="16.2818181818182" style="16" customWidth="1"/>
-    <col min="67" max="67" width="14" style="16" customWidth="1"/>
-    <col min="68" max="68" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="69" max="69" width="15" style="16" customWidth="1"/>
-    <col min="70" max="70" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="71" max="71" width="11" style="16" customWidth="1"/>
-    <col min="72" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="33" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="34" max="34" customWidth="true" style="27" width="13.5727272727273"/>
+    <col min="35" max="35" customWidth="true" style="48" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="16.0"/>
+    <col min="46" max="46" customWidth="true" style="16" width="16.8545454545455"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="18.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="18.4272727272727"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="15.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="16" width="22.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="15.5727272727273"/>
+    <col min="59" max="59" customWidth="true" style="16" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="13.0"/>
+    <col min="65" max="65" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="66" max="66" customWidth="true" style="16" width="16.2818181818182"/>
+    <col min="67" max="67" customWidth="true" style="16" width="14.0"/>
+    <col min="68" max="68" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="69" max="69" customWidth="true" style="16" width="15.0"/>
+    <col min="70" max="70" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="71" max="71" customWidth="true" style="16" width="11.0"/>
+    <col min="72" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -19960,77 +19960,77 @@
   <dimension ref="A1:BU17"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="16" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="57" max="57" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="59" max="59" width="15" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="13" style="16" customWidth="1"/>
-    <col min="65" max="65" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="66" max="66" width="9.13636363636364" style="16"/>
-    <col min="67" max="67" width="14" style="16" customWidth="1"/>
-    <col min="68" max="68" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="69" max="69" width="15" style="16" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="16"/>
-    <col min="71" max="71" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="72" max="72" width="11" style="16" customWidth="1"/>
-    <col min="73" max="73" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="74" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="16.0"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="59" max="59" customWidth="true" style="16" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="13.0"/>
+    <col min="65" max="65" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="66" max="66" style="16" width="9.13636363636364"/>
+    <col min="67" max="67" customWidth="true" style="16" width="14.0"/>
+    <col min="68" max="68" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="69" max="69" customWidth="true" style="16" width="15.0"/>
+    <col min="70" max="70" style="16" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="16" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="74" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -21331,76 +21331,76 @@
   <dimension ref="A1:BU17"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="57" max="57" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="59" max="59" width="15" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="67" width="9.13636363636364" style="16"/>
-    <col min="68" max="68" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="69" max="69" width="15" style="16" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="16"/>
-    <col min="71" max="71" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="72" max="72" width="11" style="16" customWidth="1"/>
-    <col min="73" max="73" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="74" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="59" max="59" customWidth="true" style="16" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="67" style="16" width="9.13636363636364"/>
+    <col min="68" max="68" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="69" max="69" customWidth="true" style="16" width="15.0"/>
+    <col min="70" max="70" style="16" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="16" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="74" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -22701,76 +22701,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="32" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="33" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="34" max="34" width="13.5727272727273" style="27" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="16" style="16" customWidth="1"/>
-    <col min="46" max="46" width="16.8545454545455" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="18.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="18.4272727272727" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="15.8545454545455" style="16" customWidth="1"/>
-    <col min="57" max="57" width="22.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="15.5727272727273" style="16" customWidth="1"/>
-    <col min="59" max="59" width="15" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="13" style="16" customWidth="1"/>
-    <col min="65" max="65" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="66" max="66" width="16.2818181818182" style="16" customWidth="1"/>
-    <col min="67" max="67" width="14" style="16" customWidth="1"/>
-    <col min="68" max="68" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="69" max="69" width="15" style="16" customWidth="1"/>
-    <col min="70" max="70" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="71" max="71" width="11" style="16" customWidth="1"/>
-    <col min="72" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="33" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="34" max="34" customWidth="true" style="27" width="13.5727272727273"/>
+    <col min="35" max="35" customWidth="true" style="48" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="16.0"/>
+    <col min="46" max="46" customWidth="true" style="16" width="16.8545454545455"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="18.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="18.4272727272727"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="15.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="16" width="22.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="15.5727272727273"/>
+    <col min="59" max="59" customWidth="true" style="16" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="13.0"/>
+    <col min="65" max="65" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="66" max="66" customWidth="true" style="16" width="16.2818181818182"/>
+    <col min="67" max="67" customWidth="true" style="16" width="14.0"/>
+    <col min="68" max="68" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="69" max="69" customWidth="true" style="16" width="15.0"/>
+    <col min="70" max="70" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="71" max="71" customWidth="true" style="16" width="11.0"/>
+    <col min="72" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -23816,69 +23816,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="13" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="21" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="12" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="14" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="15" style="16" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="66" width="12.1363636363636" style="16" customWidth="1"/>
-    <col min="67" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="13.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="21.0"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="12" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="14.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="15.0"/>
+    <col min="57" max="57" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="16" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="16" width="12.1363636363636"/>
+    <col min="67" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:34">
@@ -24795,76 +24795,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="57" max="57" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="59" max="59" width="15" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="67" width="9.13636363636364" style="16"/>
-    <col min="68" max="68" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="69" max="69" width="15" style="16" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="16"/>
-    <col min="71" max="71" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="72" max="72" width="11" style="16" customWidth="1"/>
-    <col min="73" max="73" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="74" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="59" max="59" customWidth="true" style="16" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="67" style="16" width="9.13636363636364"/>
+    <col min="68" max="68" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="69" max="69" customWidth="true" style="16" width="15.0"/>
+    <col min="70" max="70" style="16" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="16" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="74" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -25926,76 +25926,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="57" max="57" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="59" max="59" width="15" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="67" width="9.13636363636364" style="16"/>
-    <col min="68" max="68" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="69" max="69" width="15" style="16" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="16"/>
-    <col min="71" max="71" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="72" max="72" width="11" style="16" customWidth="1"/>
-    <col min="73" max="73" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="74" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="59" max="59" customWidth="true" style="16" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="67" style="16" width="9.13636363636364"/>
+    <col min="68" max="68" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="69" max="69" customWidth="true" style="16" width="15.0"/>
+    <col min="70" max="70" style="16" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="16" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="74" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -27059,76 +27059,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="32" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="32" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="13" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="57" max="57" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="59" max="59" width="15" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="67" width="9.13636363636364" style="16"/>
-    <col min="68" max="68" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="69" max="69" width="15" style="16" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="16"/>
-    <col min="71" max="71" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="72" max="72" width="11" style="16" customWidth="1"/>
-    <col min="73" max="73" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="74" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="32.0"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="13.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="59" max="59" customWidth="true" style="16" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="67" style="16" width="9.13636363636364"/>
+    <col min="68" max="68" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="69" max="69" customWidth="true" style="16" width="15.0"/>
+    <col min="70" max="70" style="16" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="16" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="74" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -28192,49 +28192,49 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="49" width="9.13636363636364" style="16"/>
-    <col min="50" max="50" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="9.13636363636364" style="16"/>
-    <col min="52" max="52" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="53" max="58" width="9.13636363636364" style="16"/>
-    <col min="59" max="59" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="60" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="49" style="16" width="9.13636363636364"/>
+    <col min="50" max="50" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="51" max="51" style="16" width="9.13636363636364"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="53" max="58" style="16" width="9.13636363636364"/>
+    <col min="59" max="59" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="60" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -29248,51 +29248,51 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="45" width="9.13636363636364" style="16"/>
-    <col min="46" max="46" width="12" style="16" customWidth="1"/>
-    <col min="47" max="49" width="9.13636363636364" style="16"/>
-    <col min="50" max="50" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="9.13636363636364" style="16"/>
-    <col min="52" max="52" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="53" max="58" width="9.13636363636364" style="16"/>
-    <col min="59" max="59" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="60" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="45" style="16" width="9.13636363636364"/>
+    <col min="46" max="46" customWidth="true" style="16" width="12.0"/>
+    <col min="47" max="49" style="16" width="9.13636363636364"/>
+    <col min="50" max="50" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="51" max="51" style="16" width="9.13636363636364"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="53" max="58" style="16" width="9.13636363636364"/>
+    <col min="59" max="59" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="60" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -30306,43 +30306,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -30624,7 +30624,7 @@
       <c r="G5" s="9">
         <v>11</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" t="s" s="16">
         <v>74</v>
       </c>
       <c r="I5" s="9">
@@ -30775,7 +30775,7 @@
       <c r="G6" s="9">
         <v>15</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" t="s" s="16">
         <v>75</v>
       </c>
       <c r="I6" s="9">
@@ -31009,52 +31009,52 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="49" width="9.13636363636364" style="16"/>
-    <col min="50" max="50" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="9.13636363636364" style="16"/>
-    <col min="52" max="52" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="53" max="58" width="9.13636363636364" style="16"/>
-    <col min="59" max="59" width="15" style="16" customWidth="1"/>
-    <col min="60" max="70" width="9.13636363636364" style="16"/>
-    <col min="71" max="71" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="72" max="72" width="11" style="16" customWidth="1"/>
-    <col min="73" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="49" style="16" width="9.13636363636364"/>
+    <col min="50" max="50" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="51" max="51" style="16" width="9.13636363636364"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="53" max="58" style="16" width="9.13636363636364"/>
+    <col min="59" max="59" customWidth="true" style="16" width="15.0"/>
+    <col min="60" max="70" style="16" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="16" width="11.0"/>
+    <col min="73" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -32068,69 +32068,69 @@
   <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="57" max="57" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="16" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -32806,69 +32806,69 @@
   <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="16" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="57" max="57" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="16" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -33392,69 +33392,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="13" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="21" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="12" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="14" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="15" style="16" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="66" width="12.1363636363636" style="16" customWidth="1"/>
-    <col min="67" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="13.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="21.0"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="12" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="14.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="15.0"/>
+    <col min="57" max="57" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="16" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="16" width="12.1363636363636"/>
+    <col min="67" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:34">
@@ -34373,69 +34373,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="13" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="21" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="12" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="14" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="14.1363636363636" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="15" style="16" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="66" width="12.1363636363636" style="16" customWidth="1"/>
-    <col min="67" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="13.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="21.0"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="12" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="14.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="14.1363636363636"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="15.0"/>
+    <col min="57" max="57" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="16" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="16" width="12.1363636363636"/>
+    <col min="67" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:34">
@@ -35350,69 +35350,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="13" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="21" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="12" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="14" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="66" width="12.1363636363636" style="16" customWidth="1"/>
-    <col min="67" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="13.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="21.0"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="12" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="14.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="57" max="57" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="16" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="16" width="12.1363636363636"/>
+    <col min="67" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:34">
@@ -36321,69 +36321,69 @@
   <dimension ref="A1:BN8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="13" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="21" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="16" customWidth="1"/>
-    <col min="11" max="12" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="13" style="16" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="14" style="16" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="28" max="28" width="13" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="16" customWidth="1"/>
-    <col min="42" max="42" width="15" style="16" customWidth="1"/>
-    <col min="43" max="43" width="16" style="16" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="16" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="46" max="46" width="11" style="16" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="16" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="16" customWidth="1"/>
-    <col min="52" max="52" width="13" style="16" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="16" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="16" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="16" customWidth="1"/>
-    <col min="56" max="56" width="15" style="16" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="16" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="16" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="16" customWidth="1"/>
-    <col min="63" max="63" width="15" style="16" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="65" max="65" width="11" style="16" customWidth="1"/>
-    <col min="66" max="66" width="12.1363636363636" style="16" customWidth="1"/>
-    <col min="67" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="13.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="21.0"/>
+    <col min="8" max="8" customWidth="true" style="16" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="16" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="16" width="10.2818181818182"/>
+    <col min="11" max="12" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="13" max="13" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="14.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="16" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="16" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="16" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="16" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="16" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="16" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="16" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="16" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="16" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="16" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="16" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="16" width="15.0"/>
+    <col min="57" max="57" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="16" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="16" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="16" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="16" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="16" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="16" width="12.1363636363636"/>
+    <col min="67" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:34">
@@ -37504,54 +37504,54 @@
   <dimension ref="A1:BU9"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="15" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="49" width="9.13636363636364" style="16"/>
-    <col min="50" max="50" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="51" max="51" width="9.13636363636364" style="16"/>
-    <col min="52" max="52" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="53" max="58" width="9.13636363636364" style="16"/>
-    <col min="59" max="59" width="15" style="16" customWidth="1"/>
-    <col min="60" max="67" width="9.13636363636364" style="16"/>
-    <col min="68" max="68" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="69" max="69" width="15" style="16" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="16"/>
-    <col min="71" max="71" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="72" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="49" style="16" width="9.13636363636364"/>
+    <col min="50" max="50" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="51" max="51" style="16" width="9.13636363636364"/>
+    <col min="52" max="52" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="53" max="58" style="16" width="9.13636363636364"/>
+    <col min="59" max="59" customWidth="true" style="16" width="15.0"/>
+    <col min="60" max="67" style="16" width="9.13636363636364"/>
+    <col min="68" max="68" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="69" max="69" customWidth="true" style="16" width="15.0"/>
+    <col min="70" max="70" style="16" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="72" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -38802,34 +38802,34 @@
   <dimension ref="A1:AN27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.7090909090909" customWidth="1"/>
-    <col min="4" max="4" width="28.7090909090909" customWidth="1"/>
-    <col min="5" max="5" width="10.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="17.8545454545455" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11.8545454545455" customWidth="1"/>
-    <col min="11" max="11" width="10.4272727272727" customWidth="1"/>
-    <col min="13" max="13" width="12.5727272727273" customWidth="1"/>
-    <col min="14" max="14" width="11.7090909090909" customWidth="1"/>
-    <col min="15" max="15" width="13.2818181818182" customWidth="1"/>
-    <col min="16" max="16" width="10.5727272727273" customWidth="1"/>
-    <col min="18" max="18" width="14.7090909090909" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" customWidth="1"/>
-    <col min="21" max="21" width="10.7090909090909" customWidth="1"/>
-    <col min="22" max="22" width="14" customWidth="1"/>
-    <col min="23" max="23" width="10.8545454545455" customWidth="1"/>
-    <col min="24" max="24" width="15.1363636363636" customWidth="1"/>
-    <col min="25" max="25" width="17" customWidth="1"/>
-    <col min="28" max="28" width="10.7090909090909" customWidth="1"/>
-    <col min="29" max="29" width="14.8545454545455" customWidth="1"/>
-    <col min="30" max="30" width="10.7090909090909" customWidth="1"/>
-    <col min="31" max="31" width="13.5727272727273" customWidth="1"/>
-    <col min="32" max="32" width="15.5727272727273" customWidth="1"/>
-    <col min="35" max="35" width="10" customWidth="1"/>
-    <col min="36" max="36" width="14.8545454545455" customWidth="1"/>
-    <col min="37" max="37" width="15" customWidth="1"/>
-    <col min="40" max="40" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.7090909090909"/>
+    <col min="4" max="4" customWidth="true" width="28.7090909090909"/>
+    <col min="5" max="5" customWidth="true" width="10.4272727272727"/>
+    <col min="6" max="6" customWidth="true" width="17.8545454545455"/>
+    <col min="8" max="8" customWidth="true" width="11.0"/>
+    <col min="9" max="9" customWidth="true" width="11.8545454545455"/>
+    <col min="11" max="11" customWidth="true" width="10.4272727272727"/>
+    <col min="13" max="13" customWidth="true" width="12.5727272727273"/>
+    <col min="14" max="14" customWidth="true" width="11.7090909090909"/>
+    <col min="15" max="15" customWidth="true" width="13.2818181818182"/>
+    <col min="16" max="16" customWidth="true" width="10.5727272727273"/>
+    <col min="18" max="18" customWidth="true" width="14.7090909090909"/>
+    <col min="19" max="19" customWidth="true" width="11.0"/>
+    <col min="20" max="20" customWidth="true" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" width="10.7090909090909"/>
+    <col min="22" max="22" customWidth="true" width="14.0"/>
+    <col min="23" max="23" customWidth="true" width="10.8545454545455"/>
+    <col min="24" max="24" customWidth="true" width="15.1363636363636"/>
+    <col min="25" max="25" customWidth="true" width="17.0"/>
+    <col min="28" max="28" customWidth="true" width="10.7090909090909"/>
+    <col min="29" max="29" customWidth="true" width="14.8545454545455"/>
+    <col min="30" max="30" customWidth="true" width="10.7090909090909"/>
+    <col min="31" max="31" customWidth="true" width="13.5727272727273"/>
+    <col min="32" max="32" customWidth="true" width="15.5727272727273"/>
+    <col min="35" max="35" customWidth="true" width="10.0"/>
+    <col min="36" max="36" customWidth="true" width="14.8545454545455"/>
+    <col min="37" max="37" customWidth="true" width="15.0"/>
+    <col min="40" max="40" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:39">
@@ -39209,10 +39209,10 @@
         <f>G5/AE5</f>
         <v>10</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AG5" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AH5" t="s" s="0">
         <v>55</v>
       </c>
       <c r="AI5" s="46">
@@ -39350,10 +39350,10 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>3.333</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AG6" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AH6" t="s" s="0">
         <v>64</v>
       </c>
       <c r="AI6" s="46">
@@ -40184,41 +40184,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -40500,7 +40500,7 @@
       <c r="G5" s="9">
         <v>22</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" t="s" s="16">
         <v>77</v>
       </c>
       <c r="I5" s="9">
@@ -40651,7 +40651,7 @@
       <c r="G6" s="9">
         <v>12</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" t="s" s="16">
         <v>79</v>
       </c>
       <c r="I6" s="9">
@@ -40885,45 +40885,45 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="38.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="38.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="41" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -41205,7 +41205,7 @@
       <c r="G5" s="9">
         <v>12</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" t="s" s="16">
         <v>80</v>
       </c>
       <c r="I5" s="9">
@@ -41357,7 +41357,7 @@
       <c r="G6" s="9">
         <v>14</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" t="s" s="16">
         <v>81</v>
       </c>
       <c r="I6" s="9">
@@ -41592,41 +41592,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -41908,14 +41908,14 @@
       <c r="G5" s="9">
         <v>10</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" t="s" s="16">
         <v>69</v>
       </c>
       <c r="I5" s="9">
         <f>ROUND(G5*H5,2)</f>
         <v>300</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" t="s" s="16">
         <v>62</v>
       </c>
       <c r="K5" s="9">
@@ -42059,14 +42059,14 @@
       <c r="G6" s="9">
         <v>10</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" t="s" s="16">
         <v>74</v>
       </c>
       <c r="I6" s="9">
         <f>ROUND(G6*H6,2)</f>
         <v>250</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" t="s" s="16">
         <v>52</v>
       </c>
       <c r="K6" s="9">
@@ -42293,45 +42293,45 @@
   <dimension ref="A1:AR8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="12.8545454545455" style="16" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="16"/>
-    <col min="43" max="43" width="11" style="16" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="12.8545454545455"/>
+    <col min="41" max="42" style="16" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="16" width="11.0"/>
+    <col min="44" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -43009,43 +43009,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="16" customWidth="1"/>
-    <col min="2" max="2" width="31.7090909090909" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="16" customWidth="1"/>
-    <col min="4" max="4" width="31.7090909090909" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="16" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="16" customWidth="1"/>
-    <col min="12" max="12" width="8" style="16" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="16" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="16" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="16" customWidth="1"/>
-    <col min="18" max="18" width="9" style="16" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="16" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="16" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="16" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="16" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="16" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="16" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="16" customWidth="1"/>
-    <col min="30" max="30" width="12" style="16" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="16" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="16" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="27" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="48" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="16" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="16" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="16"/>
-    <col min="40" max="40" width="11" style="16" customWidth="1"/>
-    <col min="41" max="16384" width="9.13636363636364" style="16"/>
+    <col min="1" max="1" customWidth="true" style="16" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="16" width="31.7090909090909"/>
+    <col min="3" max="3" customWidth="true" style="16" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="16" width="31.7090909090909"/>
+    <col min="5" max="5" customWidth="true" style="16" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="16" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="16" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="16" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="16" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="16" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="16" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="16" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="16" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="16" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="16" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="16" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="16" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="16" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="16" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="16" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="16" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="16" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="16" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="16" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="27" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="48" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="16" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="16" width="12.7090909090909"/>
+    <col min="38" max="39" style="16" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="16" width="11.0"/>
+    <col min="41" max="16384" style="16" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:34">
@@ -43327,14 +43327,14 @@
       <c r="G5" s="9">
         <v>10</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" t="s" s="16">
         <v>90</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
         <v>45330</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" t="s" s="16">
         <v>52</v>
       </c>
       <c r="K5" s="9">
@@ -43479,14 +43479,14 @@
       <c r="G6" s="9">
         <v>10</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" t="s" s="16">
         <v>92</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
         <v>21220</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" t="s" s="16">
         <v>62</v>
       </c>
       <c r="K6" s="9">

--- a/testdata/QA Scenario - Sales STD PRICE.xlsx
+++ b/testdata/QA Scenario - Sales STD PRICE.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4141" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4351" uniqueCount="207">
   <si>
     <t>Scenario  : Local Sales - Stock UOM and Sales UOM (Similar)   DOC NO :  SORD-2425-00089</t>
   </si>
@@ -733,6 +733,21 @@
   </si>
   <si>
     <t>Overall Amount</t>
+  </si>
+  <si>
+    <t>BOM-2627-0000070</t>
+  </si>
+  <si>
+    <t>BOM-2627-0000125</t>
+  </si>
+  <si>
+    <t>BOM-2627-0000126</t>
+  </si>
+  <si>
+    <t>BOM-2627-0000127</t>
+  </si>
+  <si>
+    <t>BOM-2627-0000128</t>
   </si>
 </sst>
 </file>
@@ -2125,43 +2140,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="32.5727272727273" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="38.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="32.5727272727273"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="38.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -2830,41 +2845,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -3533,41 +3548,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -4237,46 +4252,46 @@
   <dimension ref="A1:AR7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="44" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="45" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="41" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="45" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:44">
@@ -4799,46 +4814,46 @@
   <dimension ref="A1:AR7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="44" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="45" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="41" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="45" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:44">
@@ -5361,41 +5376,41 @@
   <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -5914,46 +5929,46 @@
   <dimension ref="A1:AR8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="44" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="45" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="41" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="45" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:44">
@@ -6631,43 +6646,43 @@
   <dimension ref="A1:AR8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="29" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="30" max="30" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="31" max="31" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="32" max="32" width="16" style="4" customWidth="1"/>
-    <col min="33" max="33" width="12" style="4" customWidth="1"/>
-    <col min="34" max="34" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="35" max="35" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="36" max="37" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="38" max="38" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="39" max="39" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="40" max="40" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="29" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="30" max="30" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="31" max="31" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="32" max="32" customWidth="true" style="4" width="16.0"/>
+    <col min="33" max="33" customWidth="true" style="4" width="12.0"/>
+    <col min="34" max="34" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="36" max="37" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="38" max="38" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="39" max="39" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="41" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:44">
@@ -7356,14 +7371,14 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.42727272727273" customWidth="1"/>
-    <col min="2" max="2" width="28.7090909090909" customWidth="1"/>
-    <col min="3" max="3" width="5" customWidth="1"/>
-    <col min="4" max="4" width="28.7090909090909" customWidth="1"/>
-    <col min="5" max="5" width="10.8545454545455" customWidth="1"/>
-    <col min="6" max="6" width="10.1363636363636" customWidth="1"/>
-    <col min="7" max="7" width="17.8545454545455" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="6.42727272727273"/>
+    <col min="2" max="2" customWidth="true" width="28.7090909090909"/>
+    <col min="3" max="3" customWidth="true" width="5.0"/>
+    <col min="4" max="4" customWidth="true" width="28.7090909090909"/>
+    <col min="5" max="5" customWidth="true" width="10.8545454545455"/>
+    <col min="6" max="6" customWidth="true" width="10.1363636363636"/>
+    <col min="7" max="7" customWidth="true" width="17.8545454545455"/>
+    <col min="8" max="8" customWidth="true" width="16.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -7393,19 +7408,19 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2">
+      <c r="A2" s="0">
         <f>'Case 1'!A5</f>
         <v>1</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" t="str" s="0">
         <f>'Case 1'!B5</f>
         <v>HK-FIFO-LOT-BATCH-10001(FG)</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <f>'Case 1'!C5</f>
         <v>0</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" t="str" s="0">
         <f>'Case 1'!D5</f>
         <v>HK-FIFO-LOT-BATCH-10001(FG)</v>
       </c>
@@ -7416,7 +7431,7 @@
         <f>'Case 1'!H5</f>
         <v>1234</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>99</v>
       </c>
       <c r="H2" s="78">
@@ -7425,19 +7440,19 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3">
+      <c r="A3" s="0">
         <f>'Case 1'!A6</f>
         <v>2</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" t="str" s="0">
         <f>'Case 1'!B6</f>
         <v>HK-FG-DISSIMILAR-10001</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <f>'Case 1'!C6</f>
         <v>0</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" t="str" s="0">
         <f>'Case 1'!D6</f>
         <v>HK-FG-DISSIMILAR-10001</v>
       </c>
@@ -7448,7 +7463,7 @@
         <f>'Case 1'!H6</f>
         <v>3214</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="0">
         <v>675</v>
       </c>
       <c r="H3" s="78">
@@ -7468,69 +7483,69 @@
   <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="57" max="57" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="4" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -8206,45 +8221,45 @@
   <dimension ref="A1:AR8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="31.7090909090909" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="31.7090909090909" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="31.7090909090909"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="31.7090909090909"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:44">
@@ -8922,41 +8937,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -9623,41 +9638,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -10326,41 +10341,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -11029,41 +11044,41 @@
   <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="14.5727272727273" style="3" customWidth="1"/>
-    <col min="36" max="36" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="37" max="37" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="14.5727272727273"/>
+    <col min="36" max="36" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="37" max="37" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -11579,43 +11594,43 @@
   <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="37" max="37" width="14.2818181818182" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="37" max="37" customWidth="true" style="4" width="14.2818181818182"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -12131,45 +12146,45 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="41" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -12836,41 +12851,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -13539,41 +13554,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -14245,43 +14260,43 @@
   <dimension ref="A1:AN8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:40">
@@ -14907,45 +14922,45 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="12.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="12.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="41" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -15614,28 +15629,28 @@
   <dimension ref="A1:AQ26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.7090909090909" customWidth="1"/>
-    <col min="4" max="4" width="28.7090909090909" customWidth="1"/>
-    <col min="5" max="5" width="10.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="17.8545454545455" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11.8545454545455" customWidth="1"/>
-    <col min="13" max="13" width="15.1363636363636" customWidth="1"/>
-    <col min="14" max="14" width="11.7090909090909" customWidth="1"/>
-    <col min="15" max="15" width="13.2818181818182" customWidth="1"/>
-    <col min="16" max="16" width="15.1363636363636" customWidth="1"/>
-    <col min="17" max="17" width="22.5727272727273" customWidth="1"/>
-    <col min="18" max="18" width="10.5727272727273" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" customWidth="1"/>
-    <col min="21" max="21" width="10.7090909090909" customWidth="1"/>
-    <col min="28" max="28" width="10.7090909090909" customWidth="1"/>
-    <col min="29" max="29" width="14.8545454545455" customWidth="1"/>
-    <col min="30" max="30" width="10.7090909090909" customWidth="1"/>
-    <col min="31" max="31" width="13.5727272727273" customWidth="1"/>
-    <col min="32" max="32" width="15.5727272727273" customWidth="1"/>
-    <col min="35" max="35" width="10" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.7090909090909"/>
+    <col min="4" max="4" customWidth="true" width="28.7090909090909"/>
+    <col min="5" max="5" customWidth="true" width="10.4272727272727"/>
+    <col min="6" max="6" customWidth="true" width="17.8545454545455"/>
+    <col min="8" max="8" customWidth="true" width="11.0"/>
+    <col min="9" max="9" customWidth="true" width="11.8545454545455"/>
+    <col min="13" max="13" customWidth="true" width="15.1363636363636"/>
+    <col min="14" max="14" customWidth="true" width="11.7090909090909"/>
+    <col min="15" max="15" customWidth="true" width="13.2818181818182"/>
+    <col min="16" max="16" customWidth="true" width="15.1363636363636"/>
+    <col min="17" max="17" customWidth="true" width="22.5727272727273"/>
+    <col min="18" max="18" customWidth="true" width="10.5727272727273"/>
+    <col min="19" max="19" customWidth="true" width="11.0"/>
+    <col min="20" max="20" customWidth="true" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" width="10.7090909090909"/>
+    <col min="29" max="29" customWidth="true" width="14.8545454545455"/>
+    <col min="30" max="30" customWidth="true" width="10.7090909090909"/>
+    <col min="31" max="31" customWidth="true" width="13.5727272727273"/>
+    <col min="32" max="32" customWidth="true" width="15.5727272727273"/>
+    <col min="35" max="35" customWidth="true" width="10.0"/>
+    <col min="37" max="37" customWidth="true" width="12.7090909090909"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:43">
@@ -16886,41 +16901,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="32.5727272727273" style="4" customWidth="1"/>
-    <col min="3" max="3" width="5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="38.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="32.5727272727273"/>
+    <col min="3" max="3" customWidth="true" style="4" width="5.0"/>
+    <col min="4" max="4" customWidth="true" style="4" width="38.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -17589,76 +17604,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="32" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="33" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="34" max="34" width="13.5727272727273" style="51" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="16" style="4" customWidth="1"/>
-    <col min="46" max="46" width="16.8545454545455" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="18.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="18.4272727272727" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="15.8545454545455" style="4" customWidth="1"/>
-    <col min="57" max="57" width="22.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="15.5727272727273" style="4" customWidth="1"/>
-    <col min="59" max="59" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="13" style="4" customWidth="1"/>
-    <col min="65" max="65" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="66" max="66" width="16.2818181818182" style="4" customWidth="1"/>
-    <col min="67" max="67" width="14" style="4" customWidth="1"/>
-    <col min="68" max="68" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="69" max="69" width="15" style="4" customWidth="1"/>
-    <col min="70" max="70" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="71" max="71" width="11" style="4" customWidth="1"/>
-    <col min="72" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="33" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="34" max="34" customWidth="true" style="51" width="13.5727272727273"/>
+    <col min="35" max="35" customWidth="true" style="3" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="16.0"/>
+    <col min="46" max="46" customWidth="true" style="4" width="16.8545454545455"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="18.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="18.4272727272727"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="15.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="4" width="22.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="15.5727272727273"/>
+    <col min="59" max="59" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="13.0"/>
+    <col min="65" max="65" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="66" max="66" customWidth="true" style="4" width="16.2818181818182"/>
+    <col min="67" max="67" customWidth="true" style="4" width="14.0"/>
+    <col min="68" max="68" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="69" max="69" customWidth="true" style="4" width="15.0"/>
+    <col min="70" max="70" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="71" max="71" customWidth="true" style="4" width="11.0"/>
+    <col min="72" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:71">
@@ -18702,76 +18717,76 @@
   <dimension ref="A1:BS17"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="32" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="33" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="34" max="34" width="13.5727272727273" style="51" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="16" style="4" customWidth="1"/>
-    <col min="46" max="46" width="16.8545454545455" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="18.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="18.4272727272727" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="15.8545454545455" style="4" customWidth="1"/>
-    <col min="57" max="57" width="22.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="15.5727272727273" style="4" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="13" style="4" customWidth="1"/>
-    <col min="65" max="65" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="66" max="66" width="16.2818181818182" style="4" customWidth="1"/>
-    <col min="67" max="67" width="14" style="4" customWidth="1"/>
-    <col min="68" max="68" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="69" max="69" width="15" style="4" customWidth="1"/>
-    <col min="70" max="70" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="71" max="71" width="11" style="4" customWidth="1"/>
-    <col min="72" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="33" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="34" max="34" customWidth="true" style="51" width="13.5727272727273"/>
+    <col min="35" max="35" customWidth="true" style="3" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="16.0"/>
+    <col min="46" max="46" customWidth="true" style="4" width="16.8545454545455"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="18.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="18.4272727272727"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="15.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="4" width="22.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="15.5727272727273"/>
+    <col min="59" max="59" customWidth="true" style="4" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="13.0"/>
+    <col min="65" max="65" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="66" max="66" customWidth="true" style="4" width="16.2818181818182"/>
+    <col min="67" max="67" customWidth="true" style="4" width="14.0"/>
+    <col min="68" max="68" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="69" max="69" customWidth="true" style="4" width="15.0"/>
+    <col min="70" max="70" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="71" max="71" customWidth="true" style="4" width="11.0"/>
+    <col min="72" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:71">
@@ -19994,76 +20009,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="32" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="33" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="34" max="34" width="13.5727272727273" style="51" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="16" style="4" customWidth="1"/>
-    <col min="46" max="46" width="16.8545454545455" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="18.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="18.4272727272727" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="15.8545454545455" style="4" customWidth="1"/>
-    <col min="57" max="57" width="22.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="15.5727272727273" style="4" customWidth="1"/>
-    <col min="59" max="59" width="15" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="13" style="4" customWidth="1"/>
-    <col min="65" max="65" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="66" max="66" width="16.2818181818182" style="4" customWidth="1"/>
-    <col min="67" max="67" width="14" style="4" customWidth="1"/>
-    <col min="68" max="68" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="69" max="69" width="15" style="4" customWidth="1"/>
-    <col min="70" max="70" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="71" max="71" width="11" style="4" customWidth="1"/>
-    <col min="72" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="33" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="34" max="34" customWidth="true" style="51" width="13.5727272727273"/>
+    <col min="35" max="35" customWidth="true" style="3" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="16.0"/>
+    <col min="46" max="46" customWidth="true" style="4" width="16.8545454545455"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="18.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="18.4272727272727"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="15.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="4" width="22.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="15.5727272727273"/>
+    <col min="59" max="59" customWidth="true" style="4" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="13.0"/>
+    <col min="65" max="65" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="66" max="66" customWidth="true" style="4" width="16.2818181818182"/>
+    <col min="67" max="67" customWidth="true" style="4" width="14.0"/>
+    <col min="68" max="68" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="69" max="69" customWidth="true" style="4" width="15.0"/>
+    <col min="70" max="70" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="71" max="71" customWidth="true" style="4" width="11.0"/>
+    <col min="72" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:71">
@@ -21109,77 +21124,77 @@
   <dimension ref="A1:BU17"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="16" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="57" max="57" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="59" max="59" width="15" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="13" style="4" customWidth="1"/>
-    <col min="65" max="65" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="66" max="66" width="9.13636363636364" style="4"/>
-    <col min="67" max="67" width="14" style="4" customWidth="1"/>
-    <col min="68" max="68" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="69" max="69" width="15" style="4" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="4"/>
-    <col min="71" max="71" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="72" max="72" width="11" style="4" customWidth="1"/>
-    <col min="73" max="73" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="74" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="16.0"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="59" max="59" customWidth="true" style="4" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="13.0"/>
+    <col min="65" max="65" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="66" max="66" style="4" width="9.13636363636364"/>
+    <col min="67" max="67" customWidth="true" style="4" width="14.0"/>
+    <col min="68" max="68" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="69" max="69" customWidth="true" style="4" width="15.0"/>
+    <col min="70" max="70" style="4" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="4" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="74" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:73">
@@ -22480,76 +22495,76 @@
   <dimension ref="A1:BU17"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="57" max="57" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="59" max="59" width="15" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="67" width="9.13636363636364" style="4"/>
-    <col min="68" max="68" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="69" max="69" width="15" style="4" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="4"/>
-    <col min="71" max="71" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="72" max="72" width="11" style="4" customWidth="1"/>
-    <col min="73" max="73" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="74" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="59" max="59" customWidth="true" style="4" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="67" style="4" width="9.13636363636364"/>
+    <col min="68" max="68" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="69" max="69" customWidth="true" style="4" width="15.0"/>
+    <col min="70" max="70" style="4" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="4" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="74" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:73">
@@ -23850,76 +23865,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="32" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="33" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="34" max="34" width="13.5727272727273" style="51" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="16" style="4" customWidth="1"/>
-    <col min="46" max="46" width="16.8545454545455" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="18.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="18.4272727272727" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="15.8545454545455" style="4" customWidth="1"/>
-    <col min="57" max="57" width="22.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="15.5727272727273" style="4" customWidth="1"/>
-    <col min="59" max="59" width="15" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="13" style="4" customWidth="1"/>
-    <col min="65" max="65" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="66" max="66" width="16.2818181818182" style="4" customWidth="1"/>
-    <col min="67" max="67" width="14" style="4" customWidth="1"/>
-    <col min="68" max="68" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="69" max="69" width="15" style="4" customWidth="1"/>
-    <col min="70" max="70" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="71" max="71" width="11" style="4" customWidth="1"/>
-    <col min="72" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="33" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="34" max="34" customWidth="true" style="51" width="13.5727272727273"/>
+    <col min="35" max="35" customWidth="true" style="3" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="16.0"/>
+    <col min="46" max="46" customWidth="true" style="4" width="16.8545454545455"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="18.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="18.4272727272727"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="15.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="4" width="22.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="15.5727272727273"/>
+    <col min="59" max="59" customWidth="true" style="4" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="13.0"/>
+    <col min="65" max="65" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="66" max="66" customWidth="true" style="4" width="16.2818181818182"/>
+    <col min="67" max="67" customWidth="true" style="4" width="14.0"/>
+    <col min="68" max="68" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="69" max="69" customWidth="true" style="4" width="15.0"/>
+    <col min="70" max="70" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="71" max="71" customWidth="true" style="4" width="11.0"/>
+    <col min="72" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:71">
@@ -24965,69 +24980,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="21" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="12" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="14" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="15" style="4" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="66" width="12.1363636363636" style="4" customWidth="1"/>
-    <col min="67" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="21.0"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="12" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="14.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="15.0"/>
+    <col min="57" max="57" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="4" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="4" width="12.1363636363636"/>
+    <col min="67" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:66">
@@ -25944,76 +25959,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="57" max="57" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="59" max="59" width="15" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="67" width="9.13636363636364" style="4"/>
-    <col min="68" max="68" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="69" max="69" width="15" style="4" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="4"/>
-    <col min="71" max="71" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="72" max="72" width="11" style="4" customWidth="1"/>
-    <col min="73" max="73" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="74" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="59" max="59" customWidth="true" style="4" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="67" style="4" width="9.13636363636364"/>
+    <col min="68" max="68" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="69" max="69" customWidth="true" style="4" width="15.0"/>
+    <col min="70" max="70" style="4" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="4" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="74" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:73">
@@ -27075,76 +27090,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="57" max="57" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="59" max="59" width="15" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="67" width="9.13636363636364" style="4"/>
-    <col min="68" max="68" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="69" max="69" width="15" style="4" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="4"/>
-    <col min="71" max="71" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="72" max="72" width="11" style="4" customWidth="1"/>
-    <col min="73" max="73" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="74" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="59" max="59" customWidth="true" style="4" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="67" style="4" width="9.13636363636364"/>
+    <col min="68" max="68" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="69" max="69" customWidth="true" style="4" width="15.0"/>
+    <col min="70" max="70" style="4" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="4" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="74" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:73">
@@ -28208,76 +28223,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="32" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="32" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="15.7090909090909" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="13" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="57" max="57" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="59" max="59" width="15" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="67" width="9.13636363636364" style="4"/>
-    <col min="68" max="68" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="69" max="69" width="15" style="4" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="4"/>
-    <col min="71" max="71" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="72" max="72" width="11" style="4" customWidth="1"/>
-    <col min="73" max="73" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="74" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="32.0"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="15.7090909090909"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="13.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="57" max="57" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="59" max="59" customWidth="true" style="4" width="15.0"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="67" style="4" width="9.13636363636364"/>
+    <col min="68" max="68" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="69" max="69" customWidth="true" style="4" width="15.0"/>
+    <col min="70" max="70" style="4" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="4" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="74" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:73">
@@ -29341,43 +29356,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -30044,49 +30059,49 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="49" width="9.13636363636364" style="4"/>
-    <col min="50" max="50" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="9.13636363636364" style="4"/>
-    <col min="52" max="52" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="53" max="58" width="9.13636363636364" style="4"/>
-    <col min="59" max="59" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="60" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="49" style="4" width="9.13636363636364"/>
+    <col min="50" max="50" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="51" max="51" style="4" width="9.13636363636364"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="53" max="58" style="4" width="9.13636363636364"/>
+    <col min="59" max="59" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="60" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:73">
@@ -31100,51 +31115,51 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="45" width="9.13636363636364" style="4"/>
-    <col min="46" max="46" width="12" style="4" customWidth="1"/>
-    <col min="47" max="49" width="9.13636363636364" style="4"/>
-    <col min="50" max="50" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="9.13636363636364" style="4"/>
-    <col min="52" max="52" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="53" max="58" width="9.13636363636364" style="4"/>
-    <col min="59" max="59" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="60" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="45" style="4" width="9.13636363636364"/>
+    <col min="46" max="46" customWidth="true" style="4" width="12.0"/>
+    <col min="47" max="49" style="4" width="9.13636363636364"/>
+    <col min="50" max="50" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="51" max="51" style="4" width="9.13636363636364"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="53" max="58" style="4" width="9.13636363636364"/>
+    <col min="59" max="59" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="60" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:73">
@@ -32158,52 +32173,52 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="49" width="9.13636363636364" style="4"/>
-    <col min="50" max="50" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="9.13636363636364" style="4"/>
-    <col min="52" max="52" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="53" max="58" width="9.13636363636364" style="4"/>
-    <col min="59" max="59" width="15" style="4" customWidth="1"/>
-    <col min="60" max="70" width="9.13636363636364" style="4"/>
-    <col min="71" max="71" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="72" max="72" width="11" style="4" customWidth="1"/>
-    <col min="73" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="49" style="4" width="9.13636363636364"/>
+    <col min="50" max="50" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="51" max="51" style="4" width="9.13636363636364"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="53" max="58" style="4" width="9.13636363636364"/>
+    <col min="59" max="59" customWidth="true" style="4" width="15.0"/>
+    <col min="60" max="70" style="4" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="72" max="72" customWidth="true" style="4" width="11.0"/>
+    <col min="73" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:73">
@@ -33217,69 +33232,69 @@
   <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="57" max="57" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="4" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -33955,69 +33970,69 @@
   <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="57" max="57" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="4" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -34541,69 +34556,69 @@
   <dimension ref="A1:AR15"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="11" customWidth="true" style="4" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="57" max="57" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="4" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:44">
@@ -34885,8 +34900,8 @@
       <c r="F5" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="23">
-        <v>10</v>
+      <c r="G5" t="s" s="4">
+        <v>95</v>
       </c>
       <c r="H5" s="23">
         <v>1234</v>
@@ -35017,7 +35032,9 @@
       <c r="AQ5" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="AR5" s="23"/>
+      <c r="AR5" t="s" s="4">
+        <v>206</v>
+      </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:44">
       <c r="A6" s="29"/>
@@ -35131,69 +35148,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="21" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="12" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="14" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="15" style="4" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="66" width="12.1363636363636" style="4" customWidth="1"/>
-    <col min="67" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="21.0"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="12" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="14.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="15.0"/>
+    <col min="57" max="57" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="4" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="4" width="12.1363636363636"/>
+    <col min="67" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:66">
@@ -36112,69 +36129,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="21" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="12" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="14" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="14.1363636363636" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="15" style="4" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="66" width="12.1363636363636" style="4" customWidth="1"/>
-    <col min="67" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="21.0"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="12" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="14.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="14.1363636363636"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="15.0"/>
+    <col min="57" max="57" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="4" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="4" width="12.1363636363636"/>
+    <col min="67" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:66">
@@ -37089,69 +37106,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="21" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="12" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="14" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="66" width="12.1363636363636" style="4" customWidth="1"/>
-    <col min="67" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="21.0"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="12" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="14.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="57" max="57" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="4" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="4" width="12.1363636363636"/>
+    <col min="67" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:66">
@@ -38060,69 +38077,69 @@
   <dimension ref="A1:BN8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="21" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.2818181818182" style="4" customWidth="1"/>
-    <col min="11" max="12" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="14" style="4" customWidth="1"/>
-    <col min="23" max="23" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="28" max="28" width="13" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="41" width="10.4272727272727" style="4" customWidth="1"/>
-    <col min="42" max="42" width="15" style="4" customWidth="1"/>
-    <col min="43" max="43" width="16" style="4" customWidth="1"/>
-    <col min="44" max="44" width="11.1363636363636" style="4" customWidth="1"/>
-    <col min="45" max="45" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="46" max="46" width="11" style="4" customWidth="1"/>
-    <col min="47" max="47" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="48" max="48" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="49" max="49" width="17.5727272727273" style="4" customWidth="1"/>
-    <col min="50" max="50" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="13.7090909090909" style="4" customWidth="1"/>
-    <col min="52" max="52" width="13" style="4" customWidth="1"/>
-    <col min="53" max="53" width="14.8545454545455" style="4" customWidth="1"/>
-    <col min="54" max="54" width="21.8545454545455" style="4" customWidth="1"/>
-    <col min="55" max="55" width="14.5727272727273" style="4" customWidth="1"/>
-    <col min="56" max="56" width="15" style="4" customWidth="1"/>
-    <col min="57" max="57" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="58" max="58" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="59" max="59" width="9.57272727272727" style="4" customWidth="1"/>
-    <col min="60" max="60" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="61" max="61" width="13.1363636363636" style="4" customWidth="1"/>
-    <col min="62" max="62" width="11.8545454545455" style="4" customWidth="1"/>
-    <col min="63" max="63" width="15" style="4" customWidth="1"/>
-    <col min="64" max="64" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="65" max="65" width="11" style="4" customWidth="1"/>
-    <col min="66" max="66" width="12.1363636363636" style="4" customWidth="1"/>
-    <col min="67" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="21.0"/>
+    <col min="8" max="8" customWidth="true" style="4" width="15.0"/>
+    <col min="9" max="9" customWidth="true" style="4" width="16.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="10.2818181818182"/>
+    <col min="11" max="12" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="13" max="13" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="15" max="15" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="13.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="14.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="28" max="28" customWidth="true" style="4" width="13.0"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="41" customWidth="true" style="4" width="10.4272727272727"/>
+    <col min="42" max="42" customWidth="true" style="4" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="4" width="16.0"/>
+    <col min="44" max="44" customWidth="true" style="4" width="11.1363636363636"/>
+    <col min="45" max="45" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="46" max="46" customWidth="true" style="4" width="11.0"/>
+    <col min="47" max="47" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="48" max="48" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="49" max="49" customWidth="true" style="4" width="17.5727272727273"/>
+    <col min="50" max="50" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="51" max="51" customWidth="true" style="4" width="13.7090909090909"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.0"/>
+    <col min="53" max="53" customWidth="true" style="4" width="14.8545454545455"/>
+    <col min="54" max="54" customWidth="true" style="4" width="21.8545454545455"/>
+    <col min="55" max="55" customWidth="true" style="4" width="14.5727272727273"/>
+    <col min="56" max="56" customWidth="true" style="4" width="15.0"/>
+    <col min="57" max="57" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="58" max="58" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="59" max="59" customWidth="true" style="4" width="9.57272727272727"/>
+    <col min="60" max="60" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="61" max="61" customWidth="true" style="4" width="13.1363636363636"/>
+    <col min="62" max="62" customWidth="true" style="4" width="11.8545454545455"/>
+    <col min="63" max="63" customWidth="true" style="4" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="65" max="65" customWidth="true" style="4" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="4" width="12.1363636363636"/>
+    <col min="67" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:66">
@@ -39243,41 +39260,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -39944,54 +39961,54 @@
   <dimension ref="A1:BU9"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="15" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="49" width="9.13636363636364" style="4"/>
-    <col min="50" max="50" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="51" max="51" width="9.13636363636364" style="4"/>
-    <col min="52" max="52" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="53" max="58" width="9.13636363636364" style="4"/>
-    <col min="59" max="59" width="15" style="4" customWidth="1"/>
-    <col min="60" max="67" width="9.13636363636364" style="4"/>
-    <col min="68" max="68" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="69" max="69" width="15" style="4" customWidth="1"/>
-    <col min="70" max="70" width="9.13636363636364" style="4"/>
-    <col min="71" max="71" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="72" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="15.0"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="49" style="4" width="9.13636363636364"/>
+    <col min="50" max="50" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="51" max="51" style="4" width="9.13636363636364"/>
+    <col min="52" max="52" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="53" max="58" style="4" width="9.13636363636364"/>
+    <col min="59" max="59" customWidth="true" style="4" width="15.0"/>
+    <col min="60" max="67" style="4" width="9.13636363636364"/>
+    <col min="68" max="68" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="69" max="69" customWidth="true" style="4" width="15.0"/>
+    <col min="70" max="70" style="4" width="9.13636363636364"/>
+    <col min="71" max="71" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="72" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:73">
@@ -41242,34 +41259,34 @@
   <dimension ref="A1:AN27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.7090909090909" customWidth="1"/>
-    <col min="4" max="4" width="28.7090909090909" customWidth="1"/>
-    <col min="5" max="5" width="10.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="17.8545454545455" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11.8545454545455" customWidth="1"/>
-    <col min="11" max="11" width="10.4272727272727" customWidth="1"/>
-    <col min="13" max="13" width="12.5727272727273" customWidth="1"/>
-    <col min="14" max="14" width="11.7090909090909" customWidth="1"/>
-    <col min="15" max="15" width="13.2818181818182" customWidth="1"/>
-    <col min="16" max="16" width="10.5727272727273" customWidth="1"/>
-    <col min="18" max="18" width="14.7090909090909" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" customWidth="1"/>
-    <col min="21" max="21" width="10.7090909090909" customWidth="1"/>
-    <col min="22" max="22" width="14" customWidth="1"/>
-    <col min="23" max="23" width="10.8545454545455" customWidth="1"/>
-    <col min="24" max="24" width="15.1363636363636" customWidth="1"/>
-    <col min="25" max="25" width="17" customWidth="1"/>
-    <col min="28" max="28" width="10.7090909090909" customWidth="1"/>
-    <col min="29" max="29" width="14.8545454545455" customWidth="1"/>
-    <col min="30" max="30" width="10.7090909090909" customWidth="1"/>
-    <col min="31" max="31" width="13.5727272727273" customWidth="1"/>
-    <col min="32" max="32" width="15.5727272727273" customWidth="1"/>
-    <col min="35" max="35" width="10" customWidth="1"/>
-    <col min="36" max="36" width="14.8545454545455" customWidth="1"/>
-    <col min="37" max="37" width="15" customWidth="1"/>
-    <col min="40" max="40" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.7090909090909"/>
+    <col min="4" max="4" customWidth="true" width="28.7090909090909"/>
+    <col min="5" max="5" customWidth="true" width="10.4272727272727"/>
+    <col min="6" max="6" customWidth="true" width="17.8545454545455"/>
+    <col min="8" max="8" customWidth="true" width="11.0"/>
+    <col min="9" max="9" customWidth="true" width="11.8545454545455"/>
+    <col min="11" max="11" customWidth="true" width="10.4272727272727"/>
+    <col min="13" max="13" customWidth="true" width="12.5727272727273"/>
+    <col min="14" max="14" customWidth="true" width="11.7090909090909"/>
+    <col min="15" max="15" customWidth="true" width="13.2818181818182"/>
+    <col min="16" max="16" customWidth="true" width="10.5727272727273"/>
+    <col min="18" max="18" customWidth="true" width="14.7090909090909"/>
+    <col min="19" max="19" customWidth="true" width="11.0"/>
+    <col min="20" max="20" customWidth="true" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" width="10.7090909090909"/>
+    <col min="22" max="22" customWidth="true" width="14.0"/>
+    <col min="23" max="23" customWidth="true" width="10.8545454545455"/>
+    <col min="24" max="24" customWidth="true" width="15.1363636363636"/>
+    <col min="25" max="25" customWidth="true" width="17.0"/>
+    <col min="28" max="28" customWidth="true" width="10.7090909090909"/>
+    <col min="29" max="29" customWidth="true" width="14.8545454545455"/>
+    <col min="30" max="30" customWidth="true" width="10.7090909090909"/>
+    <col min="31" max="31" customWidth="true" width="13.5727272727273"/>
+    <col min="32" max="32" customWidth="true" width="15.5727272727273"/>
+    <col min="35" max="35" customWidth="true" width="10.0"/>
+    <col min="36" max="36" customWidth="true" width="14.8545454545455"/>
+    <col min="37" max="37" customWidth="true" width="15.0"/>
+    <col min="40" max="40" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.5" spans="1:40">
@@ -41649,10 +41666,10 @@
         <f>G5/AE5</f>
         <v>10</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AG5" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AH5" t="s" s="0">
         <v>55</v>
       </c>
       <c r="AI5" s="28">
@@ -41790,10 +41807,10 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>3.333</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AG6" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AH6" t="s" s="0">
         <v>64</v>
       </c>
       <c r="AI6" s="28">
@@ -42624,45 +42641,45 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="38.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="38.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="41" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -43331,41 +43348,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">
@@ -44032,45 +44049,45 @@
   <dimension ref="A1:AR8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.8545454545455" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="12.8545454545455" style="4" customWidth="1"/>
-    <col min="41" max="42" width="9.13636363636364" style="4"/>
-    <col min="43" max="43" width="11" style="4" customWidth="1"/>
-    <col min="44" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="28.8545454545455"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="12.8545454545455"/>
+    <col min="41" max="42" style="4" width="9.13636363636364"/>
+    <col min="43" max="43" customWidth="true" style="4" width="11.0"/>
+    <col min="44" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:44">
@@ -44748,43 +44765,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="5.70909090909091" style="4" customWidth="1"/>
-    <col min="2" max="2" width="31.7090909090909" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.57272727272727" style="4" customWidth="1"/>
-    <col min="4" max="4" width="31.7090909090909" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1363636363636" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="10" max="11" width="8.13636363636364" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.8545454545455" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.5727272727273" style="4" customWidth="1"/>
-    <col min="16" max="16" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.70909090909091" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.8545454545455" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.8545454545455" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.5727272727273" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11.5727272727273" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.28181818181818" style="4" customWidth="1"/>
-    <col min="24" max="25" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11.2818181818182" style="4" customWidth="1"/>
-    <col min="27" max="27" width="10.7090909090909" style="4" customWidth="1"/>
-    <col min="28" max="28" width="11.7090909090909" style="4" customWidth="1"/>
-    <col min="29" max="29" width="16" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12" style="4" customWidth="1"/>
-    <col min="31" max="31" width="12.2818181818182" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.7090909090909" style="4" customWidth="1"/>
-    <col min="33" max="34" width="12.2818181818182" style="51" customWidth="1"/>
-    <col min="35" max="35" width="10.2818181818182" style="3" customWidth="1"/>
-    <col min="36" max="36" width="13.5727272727273" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.7090909090909" style="4" customWidth="1"/>
-    <col min="38" max="39" width="9.13636363636364" style="4"/>
-    <col min="40" max="40" width="11" style="4" customWidth="1"/>
-    <col min="41" max="16384" width="9.13636363636364" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="5.70909090909091"/>
+    <col min="2" max="2" customWidth="true" style="4" width="31.7090909090909"/>
+    <col min="3" max="3" customWidth="true" style="4" width="4.57272727272727"/>
+    <col min="4" max="4" customWidth="true" style="4" width="31.7090909090909"/>
+    <col min="5" max="5" customWidth="true" style="4" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="8" max="8" customWidth="true" style="4" width="10.1363636363636"/>
+    <col min="9" max="9" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="10" max="11" customWidth="true" style="4" width="8.13636363636364"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="4" width="13.8545454545455"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="15" max="15" customWidth="true" style="4" width="12.5727272727273"/>
+    <col min="16" max="16" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="17" max="17" customWidth="true" style="4" width="9.70909090909091"/>
+    <col min="18" max="18" customWidth="true" style="4" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="4" width="10.8545454545455"/>
+    <col min="20" max="20" customWidth="true" style="4" width="17.8545454545455"/>
+    <col min="21" max="21" customWidth="true" style="4" width="10.5727272727273"/>
+    <col min="22" max="22" customWidth="true" style="4" width="11.5727272727273"/>
+    <col min="23" max="23" customWidth="true" style="4" width="9.28181818181818"/>
+    <col min="24" max="25" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="26" max="26" customWidth="true" style="4" width="11.2818181818182"/>
+    <col min="27" max="27" customWidth="true" style="4" width="10.7090909090909"/>
+    <col min="28" max="28" customWidth="true" style="4" width="11.7090909090909"/>
+    <col min="29" max="29" customWidth="true" style="4" width="16.0"/>
+    <col min="30" max="30" customWidth="true" style="4" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="4" width="12.2818181818182"/>
+    <col min="32" max="32" customWidth="true" style="4" width="14.7090909090909"/>
+    <col min="33" max="34" customWidth="true" style="51" width="12.2818181818182"/>
+    <col min="35" max="35" customWidth="true" style="3" width="10.2818181818182"/>
+    <col min="36" max="36" customWidth="true" style="4" width="13.5727272727273"/>
+    <col min="37" max="37" customWidth="true" style="4" width="12.7090909090909"/>
+    <col min="38" max="39" style="4" width="9.13636363636364"/>
+    <col min="40" max="40" customWidth="true" style="4" width="11.0"/>
+    <col min="41" max="16384" style="4" width="9.13636363636364"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:43">

--- a/testdata/QA Scenario - Sales STD PRICE.xlsx
+++ b/testdata/QA Scenario - Sales STD PRICE.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4351" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4381" uniqueCount="207">
   <si>
     <t>Scenario  : Local Sales - Stock UOM and Sales UOM (Similar)   DOC NO :  SORD-2425-00089</t>
   </si>
@@ -2229,7 +2229,9 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" t="s" s="4">
+        <v>52</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -2271,8 +2273,8 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="10" t="s">
-        <v>4</v>
+      <c r="J3" t="s" s="4">
+        <v>62</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>5</v>
@@ -2458,7 +2460,7 @@
       <c r="G5" s="23">
         <v>44</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>51</v>
       </c>
       <c r="I5" s="23">
@@ -2610,7 +2612,7 @@
       <c r="G6" s="23">
         <v>53</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>61</v>
       </c>
       <c r="I6" s="23">
@@ -2932,7 +2934,9 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" t="s" s="4">
+        <v>62</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -2974,8 +2978,8 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="10" t="s">
-        <v>4</v>
+      <c r="J3" t="s" s="4">
+        <v>95</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>5</v>
@@ -3161,7 +3165,7 @@
       <c r="G5" s="23">
         <v>10</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>93</v>
       </c>
       <c r="I5" s="23">
@@ -3313,7 +3317,7 @@
       <c r="G6" s="23">
         <v>10</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>94</v>
       </c>
       <c r="I6" s="23">
@@ -9024,7 +9028,9 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" t="s" s="4">
+        <v>52</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -9066,8 +9072,8 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="10" t="s">
-        <v>4</v>
+      <c r="J3" t="s" s="4">
+        <v>62</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>5</v>
@@ -9253,7 +9259,7 @@
       <c r="G5" s="23">
         <v>5</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>68</v>
       </c>
       <c r="I5" s="23">
@@ -9404,7 +9410,7 @@
       <c r="G6" s="23">
         <v>89</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>69</v>
       </c>
       <c r="I6" s="23">
@@ -17217,7 +17223,7 @@
       <c r="G5" s="23">
         <v>21</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>71</v>
       </c>
       <c r="I5" s="23">
@@ -17369,7 +17375,7 @@
       <c r="G6" s="23">
         <v>35</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>73</v>
       </c>
       <c r="I6" s="23">
@@ -29674,7 +29680,7 @@
       <c r="G5" s="23">
         <v>11</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>74</v>
       </c>
       <c r="I5" s="23">
@@ -29825,7 +29831,7 @@
       <c r="G6" s="23">
         <v>15</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>75</v>
       </c>
       <c r="I6" s="23">
@@ -39576,7 +39582,7 @@
       <c r="G5" s="23">
         <v>22</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>77</v>
       </c>
       <c r="I5" s="23">
@@ -39727,7 +39733,7 @@
       <c r="G6" s="23">
         <v>12</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>79</v>
       </c>
       <c r="I6" s="23">
@@ -42961,7 +42967,7 @@
       <c r="G5" s="23">
         <v>12</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>80</v>
       </c>
       <c r="I5" s="23">
@@ -43113,7 +43119,7 @@
       <c r="G6" s="23">
         <v>14</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>81</v>
       </c>
       <c r="I6" s="23">
@@ -43435,7 +43441,9 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" t="s" s="4">
+        <v>62</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -43477,8 +43485,8 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="10" t="s">
-        <v>4</v>
+      <c r="J3" t="s" s="4">
+        <v>52</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>5</v>
@@ -43664,7 +43672,7 @@
       <c r="G5" s="23">
         <v>10</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>69</v>
       </c>
       <c r="I5" s="23">
@@ -43815,7 +43823,7 @@
       <c r="G6" s="23">
         <v>10</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>74</v>
       </c>
       <c r="I6" s="23">

--- a/testdata/QA Scenario - Sales STD PRICE.xlsx
+++ b/testdata/QA Scenario - Sales STD PRICE.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4146" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4174" uniqueCount="201">
   <si>
     <t>Scenario  : Local Sales - Stock UOM and Sales UOM (Similar)   DOC NO :  SORD-2425-00089</t>
   </si>
@@ -1871,14 +1871,14 @@
       <c r="G5" s="23">
         <v>44</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>51</v>
       </c>
       <c r="I5" s="23">
         <f>ROUND(G5*H5,2)</f>
         <v>73700</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" t="s" s="4">
         <v>52</v>
       </c>
       <c r="K5" s="23">
@@ -2023,14 +2023,14 @@
       <c r="G6" s="23">
         <v>53</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>61</v>
       </c>
       <c r="I6" s="23">
         <f>ROUND(G6*H6,2)</f>
         <v>171879</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" t="s" s="4">
         <v>62</v>
       </c>
       <c r="K6" s="23">
@@ -2568,14 +2568,14 @@
       <c r="G5" s="23">
         <v>10</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>91</v>
       </c>
       <c r="I5" s="23">
         <f>G5*H5</f>
         <v>21800</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" t="s" s="4">
         <v>62</v>
       </c>
       <c r="K5" s="23">
@@ -2720,14 +2720,14 @@
       <c r="G6" s="23">
         <v>10</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>92</v>
       </c>
       <c r="I6" s="23">
         <f>G6*H6</f>
         <v>31200</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" t="s" s="4">
         <v>93</v>
       </c>
       <c r="K6" s="23">
@@ -8644,14 +8644,14 @@
       <c r="G5" s="23">
         <v>5</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>68</v>
       </c>
       <c r="I5" s="23">
         <f>ROUND(G5*H5,2)</f>
         <v>120</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" t="s" s="4">
         <v>52</v>
       </c>
       <c r="K5" s="23">
@@ -8795,14 +8795,14 @@
       <c r="G6" s="23">
         <v>89</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>69</v>
       </c>
       <c r="I6" s="23">
         <f>ROUND(G6*H6,2)</f>
         <v>2670</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" t="s" s="4">
         <v>62</v>
       </c>
       <c r="K6" s="23">
@@ -16594,7 +16594,7 @@
       <c r="G5" s="23">
         <v>21</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>71</v>
       </c>
       <c r="I5" s="23">
@@ -16746,7 +16746,7 @@
       <c r="G6" s="23">
         <v>35</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>73</v>
       </c>
       <c r="I6" s="23">
@@ -29029,7 +29029,7 @@
       <c r="G5" s="23">
         <v>11</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>74</v>
       </c>
       <c r="I5" s="23">
@@ -29180,7 +29180,7 @@
       <c r="G6" s="23">
         <v>15</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>75</v>
       </c>
       <c r="I6" s="23">
@@ -38909,7 +38909,7 @@
       <c r="G5" s="23">
         <v>22</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>77</v>
       </c>
       <c r="I5" s="23">
@@ -39060,7 +39060,7 @@
       <c r="G6" s="23">
         <v>12</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>79</v>
       </c>
       <c r="I6" s="23">
@@ -42288,7 +42288,7 @@
       <c r="G5" s="23">
         <v>12</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>80</v>
       </c>
       <c r="I5" s="23">
@@ -42440,7 +42440,7 @@
       <c r="G6" s="23">
         <v>14</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>81</v>
       </c>
       <c r="I6" s="23">
@@ -42991,14 +42991,14 @@
       <c r="G5" s="23">
         <v>10</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" t="s" s="4">
         <v>69</v>
       </c>
       <c r="I5" s="23">
         <f>ROUND(G5*H5,2)</f>
         <v>300</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" t="s" s="4">
         <v>62</v>
       </c>
       <c r="K5" s="23">
@@ -43142,14 +43142,14 @@
       <c r="G6" s="23">
         <v>10</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s" s="4">
         <v>74</v>
       </c>
       <c r="I6" s="23">
         <f>ROUND(G6*H6,2)</f>
         <v>250</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" t="s" s="4">
         <v>52</v>
       </c>
       <c r="K6" s="23">

--- a/testdata/QA Scenario - Sales STD PRICE.xlsx
+++ b/testdata/QA Scenario - Sales STD PRICE.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4174" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4182" uniqueCount="201">
   <si>
     <t>Scenario  : Local Sales - Stock UOM and Sales UOM (Similar)   DOC NO :  SORD-2425-00089</t>
   </si>
